--- a/data/HeureAdmin.xlsx
+++ b/data/HeureAdmin.xlsx
@@ -5,18 +5,19 @@
   <workbookPr date1904="1"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://fwb365.sharepoint.com/sites/CPM-PrestationsAgentsCPM/Shared Documents/Prestations Agents CPM/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\deweba01\Downloads\files\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="580" documentId="11_8BA3C09E2DF16CD648EA96253F05920B2FF8C28C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6AF96442-F85F-409C-845E-36631E1C00A4}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C43EBD8-942C-4732-A3D9-C9D8A542A150}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="2026" sheetId="1" r:id="rId1"/>
+    <sheet name="2025" sheetId="2" r:id="rId1"/>
+    <sheet name="2026" sheetId="1" r:id="rId2"/>
   </sheets>
   <externalReferences>
-    <externalReference r:id="rId2"/>
+    <externalReference r:id="rId3"/>
   </externalReferences>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="34">
   <si>
     <t>Agent</t>
   </si>
@@ -192,7 +193,46 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="13">
+  <dxfs count="26">
+    <dxf>
+      <numFmt numFmtId="164" formatCode="[h]:mm"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="[h]:mm"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="[h]:mm"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="[h]:mm"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="[h]:mm"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="[h]:mm"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="[h]:mm"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="[h]:mm"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="[h]:mm"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="[h]:mm"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="[h]:mm"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="[h]:mm"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="[h]:mm"/>
+    </dxf>
     <dxf>
       <numFmt numFmtId="164" formatCode="[h]:mm"/>
     </dxf>
@@ -310,6 +350,71 @@
             <v>0.98353606226486145</v>
           </cell>
         </row>
+        <row r="19">
+          <cell r="E19" t="str">
+            <v xml:space="preserve"> </v>
+          </cell>
+        </row>
+        <row r="22">
+          <cell r="K22">
+            <v>1.8006944444444446</v>
+          </cell>
+        </row>
+        <row r="23">
+          <cell r="K23">
+            <v>1.9256944444444446</v>
+          </cell>
+        </row>
+        <row r="24">
+          <cell r="K24">
+            <v>2.0868055555555558</v>
+          </cell>
+        </row>
+        <row r="25">
+          <cell r="K25">
+            <v>1.9700396825396829</v>
+          </cell>
+        </row>
+        <row r="26">
+          <cell r="K26">
+            <v>2.0415674603174607</v>
+          </cell>
+        </row>
+        <row r="27">
+          <cell r="K27">
+            <v>2.0090277777777779</v>
+          </cell>
+        </row>
+        <row r="28">
+          <cell r="K28">
+            <v>1.6444444444444444</v>
+          </cell>
+        </row>
+        <row r="29">
+          <cell r="K29">
+            <v>1.3666666666666667</v>
+          </cell>
+        </row>
+        <row r="30">
+          <cell r="K30">
+            <v>1.351388888888889</v>
+          </cell>
+        </row>
+        <row r="31">
+          <cell r="K31">
+            <v>1.2155193236714976</v>
+          </cell>
+        </row>
+        <row r="32">
+          <cell r="K32">
+            <v>1.2696859903381643</v>
+          </cell>
+        </row>
+        <row r="33">
+          <cell r="K33">
+            <v>1.3089111365369948</v>
+          </cell>
+        </row>
       </sheetData>
       <sheetData sheetId="1">
         <row r="2">
@@ -347,6 +452,71 @@
             <v>0.59656746031746033</v>
           </cell>
         </row>
+        <row r="19">
+          <cell r="E19" t="str">
+            <v xml:space="preserve"> </v>
+          </cell>
+        </row>
+        <row r="22">
+          <cell r="K22">
+            <v>0.28541666666666665</v>
+          </cell>
+        </row>
+        <row r="23">
+          <cell r="K23">
+            <v>0.3520833333333333</v>
+          </cell>
+        </row>
+        <row r="24">
+          <cell r="K24">
+            <v>0.22430555555555554</v>
+          </cell>
+        </row>
+        <row r="25">
+          <cell r="K25">
+            <v>0.1736111111111111</v>
+          </cell>
+        </row>
+        <row r="26">
+          <cell r="K26">
+            <v>0.45833333333333331</v>
+          </cell>
+        </row>
+        <row r="27">
+          <cell r="K27">
+            <v>0.61805555555555558</v>
+          </cell>
+        </row>
+        <row r="28">
+          <cell r="K28">
+            <v>0.67500000000000004</v>
+          </cell>
+        </row>
+        <row r="29">
+          <cell r="K29">
+            <v>0.8354166666666667</v>
+          </cell>
+        </row>
+        <row r="30">
+          <cell r="K30">
+            <v>0.73472222222222228</v>
+          </cell>
+        </row>
+        <row r="31">
+          <cell r="K31">
+            <v>0.88888888888888895</v>
+          </cell>
+        </row>
+        <row r="32">
+          <cell r="K32">
+            <v>0.87013888888888902</v>
+          </cell>
+        </row>
+        <row r="33">
+          <cell r="K33">
+            <v>0.62222222222222234</v>
+          </cell>
+        </row>
       </sheetData>
       <sheetData sheetId="2">
         <row r="2">
@@ -384,6 +554,71 @@
             <v>2.0004999999999997</v>
           </cell>
         </row>
+        <row r="19">
+          <cell r="E19" t="str">
+            <v xml:space="preserve"> </v>
+          </cell>
+        </row>
+        <row r="22">
+          <cell r="K22">
+            <v>0.57013888888888886</v>
+          </cell>
+        </row>
+        <row r="23">
+          <cell r="K23">
+            <v>0.47569444444444442</v>
+          </cell>
+        </row>
+        <row r="24">
+          <cell r="K24">
+            <v>0.5215277777777777</v>
+          </cell>
+        </row>
+        <row r="25">
+          <cell r="K25">
+            <v>0.40694444444444433</v>
+          </cell>
+        </row>
+        <row r="26">
+          <cell r="K26">
+            <v>0.21527777777777768</v>
+          </cell>
+        </row>
+        <row r="27">
+          <cell r="K27">
+            <v>0.29444444444444445</v>
+          </cell>
+        </row>
+        <row r="28">
+          <cell r="K28">
+            <v>0.36527777777777781</v>
+          </cell>
+        </row>
+        <row r="29">
+          <cell r="K29">
+            <v>0.52361111111111114</v>
+          </cell>
+        </row>
+        <row r="30">
+          <cell r="K30">
+            <v>0.40869444444444447</v>
+          </cell>
+        </row>
+        <row r="31">
+          <cell r="K31">
+            <v>0.60869444444444443</v>
+          </cell>
+        </row>
+        <row r="32">
+          <cell r="K32">
+            <v>0.80452777777777773</v>
+          </cell>
+        </row>
+        <row r="33">
+          <cell r="K33">
+            <v>0.97550000000000003</v>
+          </cell>
+        </row>
       </sheetData>
       <sheetData sheetId="3">
         <row r="2">
@@ -421,6 +656,71 @@
             <v>0.83581466842336394</v>
           </cell>
         </row>
+        <row r="19">
+          <cell r="E19" t="str">
+            <v xml:space="preserve"> </v>
+          </cell>
+        </row>
+        <row r="22">
+          <cell r="K22">
+            <v>0.8472222222222221</v>
+          </cell>
+        </row>
+        <row r="23">
+          <cell r="K23">
+            <v>0.98749999999999993</v>
+          </cell>
+        </row>
+        <row r="24">
+          <cell r="K24">
+            <v>1.0777777777777777</v>
+          </cell>
+        </row>
+        <row r="25">
+          <cell r="K25">
+            <v>0.98333333333333317</v>
+          </cell>
+        </row>
+        <row r="26">
+          <cell r="K26">
+            <v>0.72499999999999987</v>
+          </cell>
+        </row>
+        <row r="27">
+          <cell r="K27">
+            <v>1.1743055555555555</v>
+          </cell>
+        </row>
+        <row r="28">
+          <cell r="K28">
+            <v>1.2520833333333332</v>
+          </cell>
+        </row>
+        <row r="29">
+          <cell r="K29">
+            <v>1.2854166666666664</v>
+          </cell>
+        </row>
+        <row r="30">
+          <cell r="K30">
+            <v>0.7965277777777775</v>
+          </cell>
+        </row>
+        <row r="31">
+          <cell r="K31">
+            <v>1.6586050724637678</v>
+          </cell>
+        </row>
+        <row r="32">
+          <cell r="K32">
+            <v>1.5919384057971011</v>
+          </cell>
+        </row>
+        <row r="33">
+          <cell r="K33">
+            <v>0.88916062801932338</v>
+          </cell>
+        </row>
       </sheetData>
       <sheetData sheetId="4">
         <row r="2">
@@ -458,6 +758,71 @@
             <v>0.99166666666666647</v>
           </cell>
         </row>
+        <row r="19">
+          <cell r="E19" t="str">
+            <v xml:space="preserve"> </v>
+          </cell>
+        </row>
+        <row r="22">
+          <cell r="K22">
+            <v>3.0395833333333337</v>
+          </cell>
+        </row>
+        <row r="23">
+          <cell r="K23">
+            <v>3.1229166666666672</v>
+          </cell>
+        </row>
+        <row r="24">
+          <cell r="K24">
+            <v>2.8506944444444451</v>
+          </cell>
+        </row>
+        <row r="25">
+          <cell r="K25">
+            <v>2.7034722222222229</v>
+          </cell>
+        </row>
+        <row r="26">
+          <cell r="K26">
+            <v>2.6715277777777784</v>
+          </cell>
+        </row>
+        <row r="27">
+          <cell r="K27">
+            <v>2.7715277777777776</v>
+          </cell>
+        </row>
+        <row r="28">
+          <cell r="K28">
+            <v>2.2312499999999997</v>
+          </cell>
+        </row>
+        <row r="29">
+          <cell r="K29">
+            <v>1.6638888888888888</v>
+          </cell>
+        </row>
+        <row r="30">
+          <cell r="K30">
+            <v>1.1506944444444445</v>
+          </cell>
+        </row>
+        <row r="31">
+          <cell r="K31">
+            <v>1.1006944444444444</v>
+          </cell>
+        </row>
+        <row r="32">
+          <cell r="K32">
+            <v>1.1763888888888889</v>
+          </cell>
+        </row>
+        <row r="33">
+          <cell r="K33">
+            <v>1.3861111111111111</v>
+          </cell>
+        </row>
       </sheetData>
       <sheetData sheetId="5">
         <row r="2">
@@ -495,6 +860,21 @@
             <v>5.2544191919191879E-2</v>
           </cell>
         </row>
+        <row r="19">
+          <cell r="E19">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="32">
+          <cell r="K32">
+            <v>5.2777777777777778E-2</v>
+          </cell>
+        </row>
+        <row r="33">
+          <cell r="K33">
+            <v>0.17083333333333334</v>
+          </cell>
+        </row>
       </sheetData>
       <sheetData sheetId="6">
         <row r="2">
@@ -532,6 +912,71 @@
             <v>0.84652118134647258</v>
           </cell>
         </row>
+        <row r="19">
+          <cell r="E19" t="str">
+            <v xml:space="preserve"> </v>
+          </cell>
+        </row>
+        <row r="22">
+          <cell r="K22">
+            <v>0.32222222222222219</v>
+          </cell>
+        </row>
+        <row r="23">
+          <cell r="K23">
+            <v>0.55902777777777768</v>
+          </cell>
+        </row>
+        <row r="24">
+          <cell r="K24">
+            <v>0.71319444444444435</v>
+          </cell>
+        </row>
+        <row r="25">
+          <cell r="K25">
+            <v>0.73541666666666661</v>
+          </cell>
+        </row>
+        <row r="26">
+          <cell r="K26">
+            <v>0.98402777777777772</v>
+          </cell>
+        </row>
+        <row r="27">
+          <cell r="K27">
+            <v>1.3493055555555558</v>
+          </cell>
+        </row>
+        <row r="28">
+          <cell r="K28">
+            <v>1.3590277777777779</v>
+          </cell>
+        </row>
+        <row r="29">
+          <cell r="K29">
+            <v>1.2263888888888892</v>
+          </cell>
+        </row>
+        <row r="30">
+          <cell r="K30">
+            <v>1.2566287878787881</v>
+          </cell>
+        </row>
+        <row r="31">
+          <cell r="K31">
+            <v>0.4358256477821697</v>
+          </cell>
+        </row>
+        <row r="32">
+          <cell r="K32">
+            <v>0.6365200922266141</v>
+          </cell>
+        </row>
+        <row r="33">
+          <cell r="K33">
+            <v>0.53944406883480123</v>
+          </cell>
+        </row>
       </sheetData>
       <sheetData sheetId="7">
         <row r="2">
@@ -569,6 +1014,71 @@
             <v>0.70000000000000018</v>
           </cell>
         </row>
+        <row r="19">
+          <cell r="E19" t="str">
+            <v xml:space="preserve"> </v>
+          </cell>
+        </row>
+        <row r="22">
+          <cell r="K22">
+            <v>0.97638888888888886</v>
+          </cell>
+        </row>
+        <row r="23">
+          <cell r="K23">
+            <v>0.97638888888888886</v>
+          </cell>
+        </row>
+        <row r="24">
+          <cell r="K24">
+            <v>1.2013888888888888</v>
+          </cell>
+        </row>
+        <row r="25">
+          <cell r="K25">
+            <v>1.3263888888888888</v>
+          </cell>
+        </row>
+        <row r="26">
+          <cell r="K26">
+            <v>1.4513888888888888</v>
+          </cell>
+        </row>
+        <row r="27">
+          <cell r="K27">
+            <v>1.7569444444444446</v>
+          </cell>
+        </row>
+        <row r="28">
+          <cell r="K28">
+            <v>1.4027777777777779</v>
+          </cell>
+        </row>
+        <row r="29">
+          <cell r="K29">
+            <v>1.2083333333333335</v>
+          </cell>
+        </row>
+        <row r="30">
+          <cell r="K30">
+            <v>1.3333333333333335</v>
+          </cell>
+        </row>
+        <row r="31">
+          <cell r="K31">
+            <v>1.4583333333333335</v>
+          </cell>
+        </row>
+        <row r="32">
+          <cell r="K32">
+            <v>1.5833333333333335</v>
+          </cell>
+        </row>
+        <row r="33">
+          <cell r="K33">
+            <v>1.7083333333333335</v>
+          </cell>
+        </row>
       </sheetData>
       <sheetData sheetId="8">
         <row r="10">
@@ -613,6 +1123,71 @@
             <v>2.4746843434343435</v>
           </cell>
         </row>
+        <row r="19">
+          <cell r="E19" t="str">
+            <v xml:space="preserve"> </v>
+          </cell>
+        </row>
+        <row r="22">
+          <cell r="K22">
+            <v>2.6381944444444443</v>
+          </cell>
+        </row>
+        <row r="23">
+          <cell r="K23">
+            <v>2.728472222222222</v>
+          </cell>
+        </row>
+        <row r="24">
+          <cell r="K24">
+            <v>2.7340277777777775</v>
+          </cell>
+        </row>
+        <row r="25">
+          <cell r="K25">
+            <v>2.2784722222222218</v>
+          </cell>
+        </row>
+        <row r="26">
+          <cell r="K26">
+            <v>2.7152777777777772</v>
+          </cell>
+        </row>
+        <row r="27">
+          <cell r="K27">
+            <v>2.8583333333333338</v>
+          </cell>
+        </row>
+        <row r="28">
+          <cell r="K28">
+            <v>2.7222222222222228</v>
+          </cell>
+        </row>
+        <row r="29">
+          <cell r="K29">
+            <v>2.4770833333333337</v>
+          </cell>
+        </row>
+        <row r="30">
+          <cell r="K30">
+            <v>2.4972222222222227</v>
+          </cell>
+        </row>
+        <row r="31">
+          <cell r="K31">
+            <v>2.3291666666666671</v>
+          </cell>
+        </row>
+        <row r="32">
+          <cell r="K32">
+            <v>2.3923611111111116</v>
+          </cell>
+        </row>
+        <row r="33">
+          <cell r="K33">
+            <v>2.6215277777777781</v>
+          </cell>
+        </row>
       </sheetData>
       <sheetData sheetId="10">
         <row r="2">
@@ -650,6 +1225,71 @@
             <v>3.3840277777777779</v>
           </cell>
         </row>
+        <row r="19">
+          <cell r="E19" t="str">
+            <v xml:space="preserve"> </v>
+          </cell>
+        </row>
+        <row r="22">
+          <cell r="K22">
+            <v>1.7541666666666667</v>
+          </cell>
+        </row>
+        <row r="23">
+          <cell r="K23">
+            <v>1.7958333333333334</v>
+          </cell>
+        </row>
+        <row r="24">
+          <cell r="K24">
+            <v>1.9722222222222223</v>
+          </cell>
+        </row>
+        <row r="25">
+          <cell r="K25">
+            <v>1.8930555555555557</v>
+          </cell>
+        </row>
+        <row r="26">
+          <cell r="K26">
+            <v>2.3131944444444446</v>
+          </cell>
+        </row>
+        <row r="27">
+          <cell r="K27">
+            <v>2.3986111111111112</v>
+          </cell>
+        </row>
+        <row r="28">
+          <cell r="K28">
+            <v>2.5736111111111111</v>
+          </cell>
+        </row>
+        <row r="29">
+          <cell r="K29">
+            <v>2.7263888888888888</v>
+          </cell>
+        </row>
+        <row r="30">
+          <cell r="K30">
+            <v>2.7513888888888887</v>
+          </cell>
+        </row>
+        <row r="31">
+          <cell r="K31">
+            <v>2.7319444444444443</v>
+          </cell>
+        </row>
+        <row r="32">
+          <cell r="K32">
+            <v>2.9680555555555554</v>
+          </cell>
+        </row>
+        <row r="33">
+          <cell r="K33">
+            <v>2.9638888888888886</v>
+          </cell>
+        </row>
       </sheetData>
       <sheetData sheetId="11">
         <row r="2">
@@ -687,6 +1327,71 @@
             <v>0.72844254080524107</v>
           </cell>
         </row>
+        <row r="19">
+          <cell r="E19" t="str">
+            <v xml:space="preserve"> </v>
+          </cell>
+        </row>
+        <row r="22">
+          <cell r="K22">
+            <v>0.40972222222222221</v>
+          </cell>
+        </row>
+        <row r="23">
+          <cell r="K23">
+            <v>0.64861111111111114</v>
+          </cell>
+        </row>
+        <row r="24">
+          <cell r="K24">
+            <v>0.54623015873015879</v>
+          </cell>
+        </row>
+        <row r="25">
+          <cell r="K25">
+            <v>0.67678571428571432</v>
+          </cell>
+        </row>
+        <row r="26">
+          <cell r="K26">
+            <v>0.86150793650793656</v>
+          </cell>
+        </row>
+        <row r="27">
+          <cell r="K27">
+            <v>0.76388888888888906</v>
+          </cell>
+        </row>
+        <row r="28">
+          <cell r="K28">
+            <v>0.69722222222222241</v>
+          </cell>
+        </row>
+        <row r="29">
+          <cell r="K29">
+            <v>0.94722222222222241</v>
+          </cell>
+        </row>
+        <row r="30">
+          <cell r="K30">
+            <v>1.1972222222222224</v>
+          </cell>
+        </row>
+        <row r="31">
+          <cell r="K31">
+            <v>1.0780193236714977</v>
+          </cell>
+        </row>
+        <row r="32">
+          <cell r="K32">
+            <v>0.69468599033816436</v>
+          </cell>
+        </row>
+        <row r="33">
+          <cell r="K33">
+            <v>0.72602370963640994</v>
+          </cell>
+        </row>
       </sheetData>
       <sheetData sheetId="12">
         <row r="9">
@@ -736,6 +1441,71 @@
             <v>1.2388520799693574</v>
           </cell>
         </row>
+        <row r="19">
+          <cell r="E19" t="str">
+            <v xml:space="preserve"> </v>
+          </cell>
+        </row>
+        <row r="22">
+          <cell r="K22">
+            <v>1.4</v>
+          </cell>
+        </row>
+        <row r="23">
+          <cell r="K23">
+            <v>1.4152777777777779</v>
+          </cell>
+        </row>
+        <row r="24">
+          <cell r="K24">
+            <v>1.5555555555555558</v>
+          </cell>
+        </row>
+        <row r="25">
+          <cell r="K25">
+            <v>1.3479166666666669</v>
+          </cell>
+        </row>
+        <row r="26">
+          <cell r="K26">
+            <v>1.4513888888888893</v>
+          </cell>
+        </row>
+        <row r="27">
+          <cell r="K27">
+            <v>1.5506944444444446</v>
+          </cell>
+        </row>
+        <row r="28">
+          <cell r="K28">
+            <v>1.5813611111111112</v>
+          </cell>
+        </row>
+        <row r="29">
+          <cell r="K29">
+            <v>1.6487222222222224</v>
+          </cell>
+        </row>
+        <row r="30">
+          <cell r="K30">
+            <v>1.6480656565656568</v>
+          </cell>
+        </row>
+        <row r="31">
+          <cell r="K31">
+            <v>1.5347806324110673</v>
+          </cell>
+        </row>
+        <row r="32">
+          <cell r="K32">
+            <v>1.6111695212999564</v>
+          </cell>
+        </row>
+        <row r="33">
+          <cell r="K33">
+            <v>1.5075876499549272</v>
+          </cell>
+        </row>
       </sheetData>
       <sheetData sheetId="14">
         <row r="2">
@@ -773,6 +1543,71 @@
             <v>0.88964646464646524</v>
           </cell>
         </row>
+        <row r="19">
+          <cell r="E19" t="str">
+            <v xml:space="preserve"> </v>
+          </cell>
+        </row>
+        <row r="22">
+          <cell r="K22">
+            <v>3.2534722222222223</v>
+          </cell>
+        </row>
+        <row r="23">
+          <cell r="K23">
+            <v>3.4138888888888892</v>
+          </cell>
+        </row>
+        <row r="24">
+          <cell r="K24">
+            <v>3.5847222222222226</v>
+          </cell>
+        </row>
+        <row r="25">
+          <cell r="K25">
+            <v>3.349305555555556</v>
+          </cell>
+        </row>
+        <row r="26">
+          <cell r="K26">
+            <v>3.5618055555555559</v>
+          </cell>
+        </row>
+        <row r="27">
+          <cell r="K27">
+            <v>3.9180555555555556</v>
+          </cell>
+        </row>
+        <row r="28">
+          <cell r="K28">
+            <v>2.5972222222222223</v>
+          </cell>
+        </row>
+        <row r="29">
+          <cell r="K29">
+            <v>0.98611111111111127</v>
+          </cell>
+        </row>
+        <row r="30">
+          <cell r="K30">
+            <v>1.0625631313131314</v>
+          </cell>
+        </row>
+        <row r="31">
+          <cell r="K31">
+            <v>1.5361742424242426</v>
+          </cell>
+        </row>
+        <row r="32">
+          <cell r="K32">
+            <v>1.6597853535353537</v>
+          </cell>
+        </row>
+        <row r="33">
+          <cell r="K33">
+            <v>1.8472853535353537</v>
+          </cell>
+        </row>
       </sheetData>
       <sheetData sheetId="15">
         <row r="2">
@@ -810,6 +1645,71 @@
             <v>0.64772727272727249</v>
           </cell>
         </row>
+        <row r="19">
+          <cell r="E19" t="str">
+            <v xml:space="preserve"> </v>
+          </cell>
+        </row>
+        <row r="22">
+          <cell r="K22">
+            <v>2.3513888888888888</v>
+          </cell>
+        </row>
+        <row r="23">
+          <cell r="K23">
+            <v>2.1055555555555552</v>
+          </cell>
+        </row>
+        <row r="24">
+          <cell r="K24">
+            <v>1.5201388888888885</v>
+          </cell>
+        </row>
+        <row r="25">
+          <cell r="K25">
+            <v>1.7604166666666663</v>
+          </cell>
+        </row>
+        <row r="26">
+          <cell r="K26">
+            <v>1.8298611111111107</v>
+          </cell>
+        </row>
+        <row r="27">
+          <cell r="K27">
+            <v>2.0874999999999999</v>
+          </cell>
+        </row>
+        <row r="28">
+          <cell r="K28">
+            <v>2.1506944444444445</v>
+          </cell>
+        </row>
+        <row r="29">
+          <cell r="K29">
+            <v>0.73541666666666661</v>
+          </cell>
+        </row>
+        <row r="30">
+          <cell r="K30">
+            <v>0.82222222222222219</v>
+          </cell>
+        </row>
+        <row r="31">
+          <cell r="K31">
+            <v>1.6166666666666667</v>
+          </cell>
+        </row>
+        <row r="32">
+          <cell r="K32">
+            <v>1.9333333333333333</v>
+          </cell>
+        </row>
+        <row r="33">
+          <cell r="K33">
+            <v>1.7097222222222221</v>
+          </cell>
+        </row>
       </sheetData>
       <sheetData sheetId="16">
         <row r="2">
@@ -847,6 +1747,71 @@
             <v>9.0388888888888896</v>
           </cell>
         </row>
+        <row r="19">
+          <cell r="E19" t="str">
+            <v xml:space="preserve"> </v>
+          </cell>
+        </row>
+        <row r="22">
+          <cell r="K22">
+            <v>3.0159722222222225</v>
+          </cell>
+        </row>
+        <row r="23">
+          <cell r="K23">
+            <v>2.7694444444444444</v>
+          </cell>
+        </row>
+        <row r="24">
+          <cell r="K24">
+            <v>2.5458333333333329</v>
+          </cell>
+        </row>
+        <row r="25">
+          <cell r="K25">
+            <v>2.9590277777777776</v>
+          </cell>
+        </row>
+        <row r="26">
+          <cell r="K26">
+            <v>2.3874999999999997</v>
+          </cell>
+        </row>
+        <row r="27">
+          <cell r="K27">
+            <v>1.9152777777777774</v>
+          </cell>
+        </row>
+        <row r="28">
+          <cell r="K28">
+            <v>1.5423611111111106</v>
+          </cell>
+        </row>
+        <row r="29">
+          <cell r="K29">
+            <v>1.6812499999999997</v>
+          </cell>
+        </row>
+        <row r="30">
+          <cell r="K30">
+            <v>3.2993055555555553</v>
+          </cell>
+        </row>
+        <row r="31">
+          <cell r="K31">
+            <v>5.374305555555555</v>
+          </cell>
+        </row>
+        <row r="32">
+          <cell r="K32">
+            <v>4.8729166666666659</v>
+          </cell>
+        </row>
+        <row r="33">
+          <cell r="K33">
+            <v>5.7562499999999996</v>
+          </cell>
+        </row>
       </sheetData>
       <sheetData sheetId="17">
         <row r="2">
@@ -884,6 +1849,71 @@
             <v>0.24758629528366369</v>
           </cell>
         </row>
+        <row r="19">
+          <cell r="E19" t="str">
+            <v xml:space="preserve"> </v>
+          </cell>
+        </row>
+        <row r="22">
+          <cell r="K22">
+            <v>0.21590909090909091</v>
+          </cell>
+        </row>
+        <row r="23">
+          <cell r="K23">
+            <v>0.21313131313131314</v>
+          </cell>
+        </row>
+        <row r="24">
+          <cell r="K24">
+            <v>3.5353535353535331E-2</v>
+          </cell>
+        </row>
+        <row r="25">
+          <cell r="K25">
+            <v>-3.6075036075036093E-2</v>
+          </cell>
+        </row>
+        <row r="26">
+          <cell r="K26">
+            <v>5.5916305916305642E-3</v>
+          </cell>
+        </row>
+        <row r="27">
+          <cell r="K27">
+            <v>0.28333333333333333</v>
+          </cell>
+        </row>
+        <row r="28">
+          <cell r="K28">
+            <v>0.22979797979797981</v>
+          </cell>
+        </row>
+        <row r="29">
+          <cell r="K29">
+            <v>0.40965909090909092</v>
+          </cell>
+        </row>
+        <row r="30">
+          <cell r="K30">
+            <v>0.43428030303030302</v>
+          </cell>
+        </row>
+        <row r="31">
+          <cell r="K31">
+            <v>0.11830808080808081</v>
+          </cell>
+        </row>
+        <row r="32">
+          <cell r="K32">
+            <v>7.1969696969697017E-3</v>
+          </cell>
+        </row>
+        <row r="33">
+          <cell r="K33">
+            <v>4.9813928761297172E-2</v>
+          </cell>
+        </row>
       </sheetData>
       <sheetData sheetId="18">
         <row r="2">
@@ -921,6 +1951,71 @@
             <v>2.3584722222222219</v>
           </cell>
         </row>
+        <row r="19">
+          <cell r="E19">
+            <v>1.1111111111111127E-2</v>
+          </cell>
+        </row>
+        <row r="22">
+          <cell r="K22">
+            <v>2.375</v>
+          </cell>
+        </row>
+        <row r="23">
+          <cell r="K23">
+            <v>2.4152777777777779</v>
+          </cell>
+        </row>
+        <row r="24">
+          <cell r="K24">
+            <v>2.5541666666666667</v>
+          </cell>
+        </row>
+        <row r="25">
+          <cell r="K25">
+            <v>2.5256944444444445</v>
+          </cell>
+        </row>
+        <row r="26">
+          <cell r="K26">
+            <v>2.4027777777777777</v>
+          </cell>
+        </row>
+        <row r="27">
+          <cell r="K27">
+            <v>2.6888888888888887</v>
+          </cell>
+        </row>
+        <row r="28">
+          <cell r="K28">
+            <v>2.7166666666666663</v>
+          </cell>
+        </row>
+        <row r="29">
+          <cell r="K29">
+            <v>2.5666666666666664</v>
+          </cell>
+        </row>
+        <row r="30">
+          <cell r="K30">
+            <v>2.5284722222222218</v>
+          </cell>
+        </row>
+        <row r="31">
+          <cell r="K31">
+            <v>2.4437499999999996</v>
+          </cell>
+        </row>
+        <row r="32">
+          <cell r="K32">
+            <v>2.4874999999999998</v>
+          </cell>
+        </row>
+        <row r="33">
+          <cell r="K33">
+            <v>2.40625</v>
+          </cell>
+        </row>
       </sheetData>
       <sheetData sheetId="19">
         <row r="2">
@@ -956,6 +2051,71 @@
         <row r="10">
           <cell r="K10">
             <v>1.1276388888888891</v>
+          </cell>
+        </row>
+        <row r="19">
+          <cell r="E19" t="str">
+            <v xml:space="preserve"> </v>
+          </cell>
+        </row>
+        <row r="22">
+          <cell r="K22">
+            <v>0.17013888888888892</v>
+          </cell>
+        </row>
+        <row r="23">
+          <cell r="K23">
+            <v>0.38611111111111118</v>
+          </cell>
+        </row>
+        <row r="24">
+          <cell r="K24">
+            <v>0.14097222222222233</v>
+          </cell>
+        </row>
+        <row r="25">
+          <cell r="K25">
+            <v>0.30208333333333348</v>
+          </cell>
+        </row>
+        <row r="26">
+          <cell r="K26">
+            <v>0.32083333333333347</v>
+          </cell>
+        </row>
+        <row r="27">
+          <cell r="K27">
+            <v>0.53472222222222221</v>
+          </cell>
+        </row>
+        <row r="28">
+          <cell r="K28">
+            <v>0.70138888888888884</v>
+          </cell>
+        </row>
+        <row r="29">
+          <cell r="K29">
+            <v>0.89861111111111103</v>
+          </cell>
+        </row>
+        <row r="30">
+          <cell r="K30">
+            <v>0.80347222222222214</v>
+          </cell>
+        </row>
+        <row r="31">
+          <cell r="K31">
+            <v>1.0284722222222222</v>
+          </cell>
+        </row>
+        <row r="32">
+          <cell r="K32">
+            <v>1.0141666666666667</v>
+          </cell>
+        </row>
+        <row r="33">
+          <cell r="K33">
+            <v>0.83450000000000002</v>
           </cell>
         </row>
       </sheetData>
@@ -965,25 +2125,50 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{4558B403-F3D3-4D48-B211-4DC3D6C66A76}" name="Tableau13" displayName="Tableau13" ref="A1:N21" totalsRowShown="0">
+  <autoFilter ref="A1:N21" xr:uid="{C7300799-99B8-4EB6-AE56-6C90EDB091F8}"/>
+  <tableColumns count="14">
+    <tableColumn id="1" xr3:uid="{EB6C97B9-1CA8-48D2-9510-545DC67E1BBF}" name="Agent"/>
+    <tableColumn id="2" xr3:uid="{C66CE8F8-4087-4061-8EA3-AB9D0A8E447C}" name="Solde 31/08" dataDxfId="12"/>
+    <tableColumn id="7" xr3:uid="{9ECC8A47-2A4B-4D34-B13F-78D39587CA33}" name="Janvier" dataDxfId="11">
+      <calculatedColumnFormula>[1]BLAVIER!$K$5</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="8" xr3:uid="{B672229B-47A9-4DDA-97B0-42F7FFE6755D}" name="Février" dataDxfId="10"/>
+    <tableColumn id="5" xr3:uid="{0D9FFA72-0E5C-462A-BC84-09657AFC2047}" name="Mars" dataDxfId="9"/>
+    <tableColumn id="6" xr3:uid="{6DD2E5EB-3749-4C8D-8925-14083FF7A139}" name="Avril" dataDxfId="8"/>
+    <tableColumn id="4" xr3:uid="{A20FEEC3-C73B-459B-97A2-74915F126C89}" name="Mai" dataDxfId="7"/>
+    <tableColumn id="3" xr3:uid="{8A000117-6DB3-4A3E-9E33-123A99327AE5}" name="Juin" dataDxfId="6"/>
+    <tableColumn id="9" xr3:uid="{0685936A-96FA-4393-87B0-7A35C9243EA4}" name="Juillet" dataDxfId="5"/>
+    <tableColumn id="10" xr3:uid="{70FA5B23-5F41-4134-AFA6-6CF2DBDA3A0B}" name="Août" dataDxfId="4"/>
+    <tableColumn id="11" xr3:uid="{5B0EE54E-7CF9-4BE7-98F7-31268BFF16C0}" name="Septembre" dataDxfId="3"/>
+    <tableColumn id="12" xr3:uid="{990F648E-0595-4475-9CA0-5C902A84D4D1}" name="Octobre" dataDxfId="2"/>
+    <tableColumn id="13" xr3:uid="{D412263F-C5F1-4334-8DE9-BAF8FA623F7F}" name="Novembre" dataDxfId="1"/>
+    <tableColumn id="14" xr3:uid="{A063487C-7F33-4DF7-8940-9A8E590D6F35}" name="Décembre" dataDxfId="0"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C7300799-99B8-4EB6-AE56-6C90EDB091F8}" name="Tableau1" displayName="Tableau1" ref="A1:N21" totalsRowShown="0">
   <autoFilter ref="A1:N21" xr:uid="{C7300799-99B8-4EB6-AE56-6C90EDB091F8}"/>
   <tableColumns count="14">
     <tableColumn id="1" xr3:uid="{404799F8-EF23-44D1-82C6-A022BF0100EC}" name="Agent"/>
-    <tableColumn id="2" xr3:uid="{921AB302-A20C-46BE-9440-9E6AB6DAFD6C}" name="Solde 31/08" dataDxfId="12"/>
-    <tableColumn id="7" xr3:uid="{E374D505-F3A4-4A54-B661-7A811C5C6CF0}" name="Janvier" dataDxfId="11">
+    <tableColumn id="2" xr3:uid="{921AB302-A20C-46BE-9440-9E6AB6DAFD6C}" name="Solde 31/08" dataDxfId="25"/>
+    <tableColumn id="7" xr3:uid="{E374D505-F3A4-4A54-B661-7A811C5C6CF0}" name="Janvier" dataDxfId="24">
       <calculatedColumnFormula>[1]BLAVIER!$K$5</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{9D8E114C-EE46-411F-8DB7-F007D2820209}" name="Février" dataDxfId="10"/>
-    <tableColumn id="5" xr3:uid="{944F841B-7157-43A7-BBF4-EE37DB90304B}" name="Mars" dataDxfId="9"/>
-    <tableColumn id="6" xr3:uid="{D6979E67-6E41-4D87-8E2F-C77EC9B86F1C}" name="Avril" dataDxfId="8"/>
-    <tableColumn id="4" xr3:uid="{73890115-5FC3-4C52-9738-5535D8C89AA6}" name="Mai" dataDxfId="7"/>
-    <tableColumn id="3" xr3:uid="{C3AD0FE6-38FB-4AF2-A2FC-CD8C6AF1D34A}" name="Juin" dataDxfId="0"/>
-    <tableColumn id="9" xr3:uid="{2CF88554-1C99-48F6-A58C-B366489DC66A}" name="Juillet" dataDxfId="6"/>
-    <tableColumn id="10" xr3:uid="{92839190-8610-4DAD-9F46-735A99F92CBC}" name="Août" dataDxfId="5"/>
-    <tableColumn id="11" xr3:uid="{29BF599E-3D07-4D08-9AF4-0E200B9474AF}" name="Septembre" dataDxfId="4"/>
-    <tableColumn id="12" xr3:uid="{69B209A5-8270-436F-A131-3A88CE5DD18E}" name="Octobre" dataDxfId="3"/>
-    <tableColumn id="13" xr3:uid="{5495805F-AD9C-4F16-87DB-C13BD64B4392}" name="Novembre" dataDxfId="2"/>
-    <tableColumn id="14" xr3:uid="{4BC933CC-966E-4C7C-A940-6828309FC481}" name="Décembre" dataDxfId="1"/>
+    <tableColumn id="8" xr3:uid="{9D8E114C-EE46-411F-8DB7-F007D2820209}" name="Février" dataDxfId="23"/>
+    <tableColumn id="5" xr3:uid="{944F841B-7157-43A7-BBF4-EE37DB90304B}" name="Mars" dataDxfId="22"/>
+    <tableColumn id="6" xr3:uid="{D6979E67-6E41-4D87-8E2F-C77EC9B86F1C}" name="Avril" dataDxfId="21"/>
+    <tableColumn id="4" xr3:uid="{73890115-5FC3-4C52-9738-5535D8C89AA6}" name="Mai" dataDxfId="20"/>
+    <tableColumn id="3" xr3:uid="{C3AD0FE6-38FB-4AF2-A2FC-CD8C6AF1D34A}" name="Juin" dataDxfId="19"/>
+    <tableColumn id="9" xr3:uid="{2CF88554-1C99-48F6-A58C-B366489DC66A}" name="Juillet" dataDxfId="18"/>
+    <tableColumn id="10" xr3:uid="{92839190-8610-4DAD-9F46-735A99F92CBC}" name="Août" dataDxfId="17"/>
+    <tableColumn id="11" xr3:uid="{29BF599E-3D07-4D08-9AF4-0E200B9474AF}" name="Septembre" dataDxfId="16"/>
+    <tableColumn id="12" xr3:uid="{69B209A5-8270-436F-A131-3A88CE5DD18E}" name="Octobre" dataDxfId="15"/>
+    <tableColumn id="13" xr3:uid="{5495805F-AD9C-4F16-87DB-C13BD64B4392}" name="Novembre" dataDxfId="14"/>
+    <tableColumn id="14" xr3:uid="{4BC933CC-966E-4C7C-A940-6828309FC481}" name="Décembre" dataDxfId="13"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1251,6 +2436,1191 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B3AD31F8-20DB-4618-AEA0-EFA9D3B91948}">
+  <dimension ref="A1:N21"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="23.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="7.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="6.85546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.7109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="7.5703125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="12.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1" t="s">
+        <v>8</v>
+      </c>
+      <c r="K1" t="s">
+        <v>9</v>
+      </c>
+      <c r="L1" t="s">
+        <v>10</v>
+      </c>
+      <c r="M1" t="s">
+        <v>11</v>
+      </c>
+      <c r="N1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B2" s="1" t="str">
+        <f>[1]BECKERS!$E$19</f>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="C2" s="1">
+        <f>[1]BECKERS!$K$22</f>
+        <v>1.8006944444444446</v>
+      </c>
+      <c r="D2" s="1">
+        <f>[1]BECKERS!$K$23</f>
+        <v>1.9256944444444446</v>
+      </c>
+      <c r="E2" s="1">
+        <f>[1]BECKERS!$K$24</f>
+        <v>2.0868055555555558</v>
+      </c>
+      <c r="F2" s="1">
+        <f>[1]BECKERS!$K$25</f>
+        <v>1.9700396825396829</v>
+      </c>
+      <c r="G2" s="1">
+        <f>[1]BECKERS!$K$26</f>
+        <v>2.0415674603174607</v>
+      </c>
+      <c r="H2" s="1">
+        <f>[1]BECKERS!$K$27</f>
+        <v>2.0090277777777779</v>
+      </c>
+      <c r="I2" s="1">
+        <f>[1]BECKERS!$K$28</f>
+        <v>1.6444444444444444</v>
+      </c>
+      <c r="J2" s="1">
+        <f>[1]BECKERS!$K$29</f>
+        <v>1.3666666666666667</v>
+      </c>
+      <c r="K2" s="1">
+        <f>[1]BECKERS!$K$30</f>
+        <v>1.351388888888889</v>
+      </c>
+      <c r="L2" s="1">
+        <f>[1]BECKERS!$K$31</f>
+        <v>1.2155193236714976</v>
+      </c>
+      <c r="M2" s="1">
+        <f>[1]BECKERS!$K$32</f>
+        <v>1.2696859903381643</v>
+      </c>
+      <c r="N2" s="1">
+        <f>[1]BECKERS!$K$33</f>
+        <v>1.3089111365369948</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B3" s="1" t="str">
+        <f>[1]BLAVIER!$E$19</f>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="C3" s="1">
+        <f>[1]BLAVIER!$K$22</f>
+        <v>0.28541666666666665</v>
+      </c>
+      <c r="D3" s="1">
+        <f>[1]BLAVIER!$K$23</f>
+        <v>0.3520833333333333</v>
+      </c>
+      <c r="E3" s="1">
+        <f>[1]BLAVIER!$K$24</f>
+        <v>0.22430555555555554</v>
+      </c>
+      <c r="F3" s="1">
+        <f>[1]BLAVIER!$K$25</f>
+        <v>0.1736111111111111</v>
+      </c>
+      <c r="G3" s="1">
+        <f>[1]BLAVIER!$K$26</f>
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="H3" s="1">
+        <f>[1]BLAVIER!$K$27</f>
+        <v>0.61805555555555558</v>
+      </c>
+      <c r="I3" s="1">
+        <f>[1]BLAVIER!$K$28</f>
+        <v>0.67500000000000004</v>
+      </c>
+      <c r="J3" s="1">
+        <f>[1]BLAVIER!$K$29</f>
+        <v>0.8354166666666667</v>
+      </c>
+      <c r="K3" s="1">
+        <f>[1]BLAVIER!$K$30</f>
+        <v>0.73472222222222228</v>
+      </c>
+      <c r="L3" s="1">
+        <f>[1]BLAVIER!$K$31</f>
+        <v>0.88888888888888895</v>
+      </c>
+      <c r="M3" s="1">
+        <f>[1]BLAVIER!$K$32</f>
+        <v>0.87013888888888902</v>
+      </c>
+      <c r="N3" s="1">
+        <f>[1]BLAVIER!$K$33</f>
+        <v>0.62222222222222234</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" s="1" t="str">
+        <f>[1]BREUCKER!$E$19</f>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="C4" s="1">
+        <f>[1]BREUCKER!$K$22</f>
+        <v>0.57013888888888886</v>
+      </c>
+      <c r="D4" s="1">
+        <f>[1]BREUCKER!$K$23</f>
+        <v>0.47569444444444442</v>
+      </c>
+      <c r="E4" s="1">
+        <f>[1]BREUCKER!$K$24</f>
+        <v>0.5215277777777777</v>
+      </c>
+      <c r="F4" s="1">
+        <f>[1]BREUCKER!$K$25</f>
+        <v>0.40694444444444433</v>
+      </c>
+      <c r="G4" s="1">
+        <f>[1]BREUCKER!$K$26</f>
+        <v>0.21527777777777768</v>
+      </c>
+      <c r="H4" s="1">
+        <f>[1]BREUCKER!$K$27</f>
+        <v>0.29444444444444445</v>
+      </c>
+      <c r="I4" s="1">
+        <f>[1]BREUCKER!$K$28</f>
+        <v>0.36527777777777781</v>
+      </c>
+      <c r="J4" s="1">
+        <f>[1]BREUCKER!$K$29</f>
+        <v>0.52361111111111114</v>
+      </c>
+      <c r="K4" s="1">
+        <f>[1]BREUCKER!$K$30</f>
+        <v>0.40869444444444447</v>
+      </c>
+      <c r="L4" s="1">
+        <f>[1]BREUCKER!$K$31</f>
+        <v>0.60869444444444443</v>
+      </c>
+      <c r="M4" s="1">
+        <f>[1]BREUCKER!$K$32</f>
+        <v>0.80452777777777773</v>
+      </c>
+      <c r="N4" s="1">
+        <f>[1]BREUCKER!$K$33</f>
+        <v>0.97550000000000003</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5" s="1" t="str">
+        <f>[1]BRUNIN!$E$19</f>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="C5" s="1">
+        <f>[1]BRUNIN!$K$22</f>
+        <v>0.8472222222222221</v>
+      </c>
+      <c r="D5" s="1">
+        <f>[1]BRUNIN!$K$23</f>
+        <v>0.98749999999999993</v>
+      </c>
+      <c r="E5" s="1">
+        <f>[1]BRUNIN!$K$24</f>
+        <v>1.0777777777777777</v>
+      </c>
+      <c r="F5" s="1">
+        <f>[1]BRUNIN!$K$25</f>
+        <v>0.98333333333333317</v>
+      </c>
+      <c r="G5" s="1">
+        <f>[1]BRUNIN!$K$26</f>
+        <v>0.72499999999999987</v>
+      </c>
+      <c r="H5" s="1">
+        <f>[1]BRUNIN!$K$27</f>
+        <v>1.1743055555555555</v>
+      </c>
+      <c r="I5" s="1">
+        <f>[1]BRUNIN!$K$28</f>
+        <v>1.2520833333333332</v>
+      </c>
+      <c r="J5" s="1">
+        <f>[1]BRUNIN!$K$29</f>
+        <v>1.2854166666666664</v>
+      </c>
+      <c r="K5" s="1">
+        <f>[1]BRUNIN!$K$30</f>
+        <v>0.7965277777777775</v>
+      </c>
+      <c r="L5" s="1">
+        <f>[1]BRUNIN!$K$31</f>
+        <v>1.6586050724637678</v>
+      </c>
+      <c r="M5" s="1">
+        <f>[1]BRUNIN!$K$32</f>
+        <v>1.5919384057971011</v>
+      </c>
+      <c r="N5" s="1">
+        <f>[1]BRUNIN!$K$33</f>
+        <v>0.88916062801932338</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>16</v>
+      </c>
+      <c r="B6" s="1" t="str">
+        <f>[1]DEWEZ!$E$19</f>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="C6" s="1">
+        <f>[1]DEWEZ!$K$22</f>
+        <v>3.0395833333333337</v>
+      </c>
+      <c r="D6" s="1">
+        <f>[1]DEWEZ!$K$23</f>
+        <v>3.1229166666666672</v>
+      </c>
+      <c r="E6" s="1">
+        <f>[1]DEWEZ!$K$24</f>
+        <v>2.8506944444444451</v>
+      </c>
+      <c r="F6" s="1">
+        <f>[1]DEWEZ!$K$25</f>
+        <v>2.7034722222222229</v>
+      </c>
+      <c r="G6" s="1">
+        <f>[1]DEWEZ!$K$26</f>
+        <v>2.6715277777777784</v>
+      </c>
+      <c r="H6" s="1">
+        <f>[1]DEWEZ!$K$27</f>
+        <v>2.7715277777777776</v>
+      </c>
+      <c r="I6" s="1">
+        <f>[1]DEWEZ!$K$28</f>
+        <v>2.2312499999999997</v>
+      </c>
+      <c r="J6" s="1">
+        <f>[1]DEWEZ!$K$29</f>
+        <v>1.6638888888888888</v>
+      </c>
+      <c r="K6" s="1">
+        <f>[1]DEWEZ!$K$30</f>
+        <v>1.1506944444444445</v>
+      </c>
+      <c r="L6" s="1">
+        <f>[1]DEWEZ!$K$31</f>
+        <v>1.1006944444444444</v>
+      </c>
+      <c r="M6" s="1">
+        <f>[1]DEWEZ!$K$32</f>
+        <v>1.1763888888888889</v>
+      </c>
+      <c r="N6" s="1">
+        <f>[1]DEWEZ!$K$33</f>
+        <v>1.3861111111111111</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>31</v>
+      </c>
+      <c r="B7" s="1">
+        <f>[1]HENDRICKX!$E$19</f>
+        <v>0</v>
+      </c>
+      <c r="C7" s="1">
+        <f>[1]HENDRICKX!$K$22</f>
+        <v>0</v>
+      </c>
+      <c r="D7" s="1">
+        <f>[1]HENDRICKX!$K$23</f>
+        <v>0</v>
+      </c>
+      <c r="E7" s="1">
+        <f>[1]HENDRICKX!$K$24</f>
+        <v>0</v>
+      </c>
+      <c r="F7" s="1">
+        <f>[1]HENDRICKX!$K$25</f>
+        <v>0</v>
+      </c>
+      <c r="G7" s="1">
+        <f>[1]HENDRICKX!$K$26</f>
+        <v>0</v>
+      </c>
+      <c r="H7" s="1">
+        <f>[1]HENDRICKX!$K$27</f>
+        <v>0</v>
+      </c>
+      <c r="I7" s="1">
+        <f>[1]HENDRICKX!$K$28</f>
+        <v>0</v>
+      </c>
+      <c r="J7" s="1">
+        <f>[1]HENDRICKX!$K$29</f>
+        <v>0</v>
+      </c>
+      <c r="K7" s="1">
+        <f>[1]HENDRICKX!$K$30</f>
+        <v>0</v>
+      </c>
+      <c r="L7" s="1">
+        <f>[1]HENDRICKX!$K$31</f>
+        <v>0</v>
+      </c>
+      <c r="M7" s="1">
+        <f>[1]HENDRICKX!$K$32</f>
+        <v>5.2777777777777778E-2</v>
+      </c>
+      <c r="N7" s="1">
+        <f>[1]HENDRICKX!$K$33</f>
+        <v>0.17083333333333334</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>17</v>
+      </c>
+      <c r="B8" s="1" t="str">
+        <f>[1]HOEBEKE!$E$19</f>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="C8" s="1">
+        <f>[1]HOEBEKE!$K$22</f>
+        <v>0.32222222222222219</v>
+      </c>
+      <c r="D8" s="1">
+        <f>[1]HOEBEKE!$K$23</f>
+        <v>0.55902777777777768</v>
+      </c>
+      <c r="E8" s="1">
+        <f>[1]HOEBEKE!$K$24</f>
+        <v>0.71319444444444435</v>
+      </c>
+      <c r="F8" s="1">
+        <f>[1]HOEBEKE!$K$25</f>
+        <v>0.73541666666666661</v>
+      </c>
+      <c r="G8" s="1">
+        <f>[1]HOEBEKE!$K$26</f>
+        <v>0.98402777777777772</v>
+      </c>
+      <c r="H8" s="1">
+        <f>[1]HOEBEKE!$K$27</f>
+        <v>1.3493055555555558</v>
+      </c>
+      <c r="I8" s="1">
+        <f>[1]HOEBEKE!$K$28</f>
+        <v>1.3590277777777779</v>
+      </c>
+      <c r="J8" s="1">
+        <f>[1]HOEBEKE!$K$29</f>
+        <v>1.2263888888888892</v>
+      </c>
+      <c r="K8" s="1">
+        <f>[1]HOEBEKE!$K$30</f>
+        <v>1.2566287878787881</v>
+      </c>
+      <c r="L8" s="1">
+        <f>[1]HOEBEKE!$K$31</f>
+        <v>0.4358256477821697</v>
+      </c>
+      <c r="M8" s="1">
+        <f>[1]HOEBEKE!$K$32</f>
+        <v>0.6365200922266141</v>
+      </c>
+      <c r="N8" s="1">
+        <f>[1]HOEBEKE!$K$33</f>
+        <v>0.53944406883480123</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>18</v>
+      </c>
+      <c r="B9" s="1" t="str">
+        <f>[1]JOIRIS!$E$19</f>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="C9" s="1">
+        <f>[1]JOIRIS!$K$22</f>
+        <v>0.97638888888888886</v>
+      </c>
+      <c r="D9" s="1">
+        <f>[1]JOIRIS!$K$23</f>
+        <v>0.97638888888888886</v>
+      </c>
+      <c r="E9" s="1">
+        <f>[1]JOIRIS!$K$24</f>
+        <v>1.2013888888888888</v>
+      </c>
+      <c r="F9" s="1">
+        <f>[1]JOIRIS!$K$25</f>
+        <v>1.3263888888888888</v>
+      </c>
+      <c r="G9" s="1">
+        <f>[1]JOIRIS!$K$26</f>
+        <v>1.4513888888888888</v>
+      </c>
+      <c r="H9" s="1">
+        <f>[1]JOIRIS!$K$27</f>
+        <v>1.7569444444444446</v>
+      </c>
+      <c r="I9" s="1">
+        <f>[1]JOIRIS!$K$28</f>
+        <v>1.4027777777777779</v>
+      </c>
+      <c r="J9" s="1">
+        <f>[1]JOIRIS!$K$29</f>
+        <v>1.2083333333333335</v>
+      </c>
+      <c r="K9" s="1">
+        <f>[1]JOIRIS!$K$30</f>
+        <v>1.3333333333333335</v>
+      </c>
+      <c r="L9" s="1">
+        <f>[1]JOIRIS!$K$31</f>
+        <v>1.4583333333333335</v>
+      </c>
+      <c r="M9" s="1">
+        <f>[1]JOIRIS!$K$32</f>
+        <v>1.5833333333333335</v>
+      </c>
+      <c r="N9" s="1">
+        <f>[1]JOIRIS!$K$33</f>
+        <v>1.7083333333333335</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>33</v>
+      </c>
+      <c r="B10" s="1">
+        <f>[1]KAISER!$E$19</f>
+        <v>0</v>
+      </c>
+      <c r="C10" s="1"/>
+      <c r="D10" s="1"/>
+      <c r="E10" s="1"/>
+      <c r="F10" s="1"/>
+      <c r="G10" s="1"/>
+      <c r="H10" s="1">
+        <f>[1]KAISER!$K$27</f>
+        <v>0</v>
+      </c>
+      <c r="I10" s="1">
+        <f>[1]KAISER!$K$28</f>
+        <v>0</v>
+      </c>
+      <c r="J10" s="1">
+        <f>[1]KAISER!$K$29</f>
+        <v>0</v>
+      </c>
+      <c r="K10" s="1">
+        <f>[1]KAISER!$K$30</f>
+        <v>0</v>
+      </c>
+      <c r="L10" s="1">
+        <f>[1]KAISER!$K$31</f>
+        <v>0</v>
+      </c>
+      <c r="M10" s="1">
+        <f>[1]KAISER!$K$32</f>
+        <v>0</v>
+      </c>
+      <c r="N10" s="1">
+        <f>[1]KAISER!$K$33</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>19</v>
+      </c>
+      <c r="B11" s="1" t="str">
+        <f>[1]LAMBERT!$E$19</f>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="C11" s="1">
+        <f>[1]LAMBERT!$K$22</f>
+        <v>2.6381944444444443</v>
+      </c>
+      <c r="D11" s="1">
+        <f>[1]LAMBERT!$K$23</f>
+        <v>2.728472222222222</v>
+      </c>
+      <c r="E11" s="1">
+        <f>[1]LAMBERT!$K$24</f>
+        <v>2.7340277777777775</v>
+      </c>
+      <c r="F11" s="1">
+        <f>[1]LAMBERT!$K$25</f>
+        <v>2.2784722222222218</v>
+      </c>
+      <c r="G11" s="1">
+        <f>[1]LAMBERT!$K$26</f>
+        <v>2.7152777777777772</v>
+      </c>
+      <c r="H11" s="1">
+        <f>[1]LAMBERT!$K$27</f>
+        <v>2.8583333333333338</v>
+      </c>
+      <c r="I11" s="1">
+        <f>[1]LAMBERT!$K$28</f>
+        <v>2.7222222222222228</v>
+      </c>
+      <c r="J11" s="1">
+        <f>[1]LAMBERT!$K$29</f>
+        <v>2.4770833333333337</v>
+      </c>
+      <c r="K11" s="1">
+        <f>[1]LAMBERT!$K$30</f>
+        <v>2.4972222222222227</v>
+      </c>
+      <c r="L11" s="1">
+        <f>[1]LAMBERT!$K$31</f>
+        <v>2.3291666666666671</v>
+      </c>
+      <c r="M11" s="1">
+        <f>[1]LAMBERT!$K$32</f>
+        <v>2.3923611111111116</v>
+      </c>
+      <c r="N11" s="1">
+        <f>[1]LAMBERT!$K$33</f>
+        <v>2.6215277777777781</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>20</v>
+      </c>
+      <c r="B12" s="1" t="str">
+        <f>[1]LEBOUTTE!$E$19</f>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="C12" s="1">
+        <f>[1]LEBOUTTE!$K$22</f>
+        <v>1.7541666666666667</v>
+      </c>
+      <c r="D12" s="1">
+        <f>[1]LEBOUTTE!$K$23</f>
+        <v>1.7958333333333334</v>
+      </c>
+      <c r="E12" s="1">
+        <f>[1]LEBOUTTE!$K$24</f>
+        <v>1.9722222222222223</v>
+      </c>
+      <c r="F12" s="1">
+        <f>[1]LEBOUTTE!$K$25</f>
+        <v>1.8930555555555557</v>
+      </c>
+      <c r="G12" s="1">
+        <f>[1]LEBOUTTE!$K$26</f>
+        <v>2.3131944444444446</v>
+      </c>
+      <c r="H12" s="1">
+        <f>[1]LEBOUTTE!$K$27</f>
+        <v>2.3986111111111112</v>
+      </c>
+      <c r="I12" s="1">
+        <f>[1]LEBOUTTE!$K$28</f>
+        <v>2.5736111111111111</v>
+      </c>
+      <c r="J12" s="1">
+        <f>[1]LEBOUTTE!$K$29</f>
+        <v>2.7263888888888888</v>
+      </c>
+      <c r="K12" s="1">
+        <f>[1]LEBOUTTE!$K$30</f>
+        <v>2.7513888888888887</v>
+      </c>
+      <c r="L12" s="1">
+        <f>[1]LEBOUTTE!$K$31</f>
+        <v>2.7319444444444443</v>
+      </c>
+      <c r="M12" s="1">
+        <f>[1]LEBOUTTE!$K$32</f>
+        <v>2.9680555555555554</v>
+      </c>
+      <c r="N12" s="1">
+        <f>[1]LEBOUTTE!$K$33</f>
+        <v>2.9638888888888886</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>21</v>
+      </c>
+      <c r="B13" s="1" t="str">
+        <f>[1]MAGNUS!$E$19</f>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="C13" s="1">
+        <f>[1]MAGNUS!$K$22</f>
+        <v>0.40972222222222221</v>
+      </c>
+      <c r="D13" s="1">
+        <f>[1]MAGNUS!$K$23</f>
+        <v>0.64861111111111114</v>
+      </c>
+      <c r="E13" s="1">
+        <f>[1]MAGNUS!$K$24</f>
+        <v>0.54623015873015879</v>
+      </c>
+      <c r="F13" s="1">
+        <f>[1]MAGNUS!$K$25</f>
+        <v>0.67678571428571432</v>
+      </c>
+      <c r="G13" s="1">
+        <f>[1]MAGNUS!$K$26</f>
+        <v>0.86150793650793656</v>
+      </c>
+      <c r="H13" s="1">
+        <f>[1]MAGNUS!$K$27</f>
+        <v>0.76388888888888906</v>
+      </c>
+      <c r="I13" s="1">
+        <f>[1]MAGNUS!$K$28</f>
+        <v>0.69722222222222241</v>
+      </c>
+      <c r="J13" s="1">
+        <f>[1]MAGNUS!$K$29</f>
+        <v>0.94722222222222241</v>
+      </c>
+      <c r="K13" s="1">
+        <f>[1]MAGNUS!$K$30</f>
+        <v>1.1972222222222224</v>
+      </c>
+      <c r="L13" s="1">
+        <f>[1]MAGNUS!$K$31</f>
+        <v>1.0780193236714977</v>
+      </c>
+      <c r="M13" s="1">
+        <f>[1]MAGNUS!$K$32</f>
+        <v>0.69468599033816436</v>
+      </c>
+      <c r="N13" s="1">
+        <f>[1]MAGNUS!$K$33</f>
+        <v>0.72602370963640994</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>32</v>
+      </c>
+      <c r="B14" s="1">
+        <f>[1]NDEMA!$E$19</f>
+        <v>0</v>
+      </c>
+      <c r="C14" s="1"/>
+      <c r="D14" s="1"/>
+      <c r="E14" s="1"/>
+      <c r="F14" s="1"/>
+      <c r="G14" s="1">
+        <f>[1]NDEMA!$K$26</f>
+        <v>0</v>
+      </c>
+      <c r="H14" s="1">
+        <f>[1]NDEMA!$K$27</f>
+        <v>0</v>
+      </c>
+      <c r="I14" s="1">
+        <f>[1]NDEMA!$K$28</f>
+        <v>0</v>
+      </c>
+      <c r="J14" s="1">
+        <f>[1]NDEMA!$K$29</f>
+        <v>0</v>
+      </c>
+      <c r="K14" s="1">
+        <f>[1]NDEMA!$K$30</f>
+        <v>0</v>
+      </c>
+      <c r="L14" s="1">
+        <f>[1]NDEMA!$K$31</f>
+        <v>0</v>
+      </c>
+      <c r="M14" s="1">
+        <f>[1]NDEMA!$K$32</f>
+        <v>0</v>
+      </c>
+      <c r="N14" s="1">
+        <f>[1]NDEMA!$K$33</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>22</v>
+      </c>
+      <c r="B15" s="1" t="str">
+        <f>[1]NOLET!$E$19</f>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="C15" s="1">
+        <f>[1]NOLET!$K$22</f>
+        <v>1.4</v>
+      </c>
+      <c r="D15" s="1">
+        <f>[1]NOLET!$K$23</f>
+        <v>1.4152777777777779</v>
+      </c>
+      <c r="E15" s="1">
+        <f>[1]NOLET!$K$24</f>
+        <v>1.5555555555555558</v>
+      </c>
+      <c r="F15" s="1">
+        <f>[1]NOLET!$K$25</f>
+        <v>1.3479166666666669</v>
+      </c>
+      <c r="G15" s="1">
+        <f>[1]NOLET!$K$26</f>
+        <v>1.4513888888888893</v>
+      </c>
+      <c r="H15" s="1">
+        <f>[1]NOLET!$K$27</f>
+        <v>1.5506944444444446</v>
+      </c>
+      <c r="I15" s="1">
+        <f>[1]NOLET!$K$28</f>
+        <v>1.5813611111111112</v>
+      </c>
+      <c r="J15" s="1">
+        <f>[1]NOLET!$K$29</f>
+        <v>1.6487222222222224</v>
+      </c>
+      <c r="K15" s="1">
+        <f>[1]NOLET!$K$30</f>
+        <v>1.6480656565656568</v>
+      </c>
+      <c r="L15" s="1">
+        <f>[1]NOLET!$K$31</f>
+        <v>1.5347806324110673</v>
+      </c>
+      <c r="M15" s="1">
+        <f>[1]NOLET!$K$32</f>
+        <v>1.6111695212999564</v>
+      </c>
+      <c r="N15" s="1">
+        <f>[1]NOLET!$K$33</f>
+        <v>1.5075876499549272</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>23</v>
+      </c>
+      <c r="B16" s="1" t="str">
+        <f>[1]PAQUAY!$E$19</f>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="C16" s="1">
+        <f>[1]PAQUAY!$K$22</f>
+        <v>3.2534722222222223</v>
+      </c>
+      <c r="D16" s="1">
+        <f>[1]PAQUAY!$K$23</f>
+        <v>3.4138888888888892</v>
+      </c>
+      <c r="E16" s="1">
+        <f>[1]PAQUAY!$K$24</f>
+        <v>3.5847222222222226</v>
+      </c>
+      <c r="F16" s="1">
+        <f>[1]PAQUAY!$K$25</f>
+        <v>3.349305555555556</v>
+      </c>
+      <c r="G16" s="1">
+        <f>[1]PAQUAY!$K$26</f>
+        <v>3.5618055555555559</v>
+      </c>
+      <c r="H16" s="1">
+        <f>[1]PAQUAY!$K$27</f>
+        <v>3.9180555555555556</v>
+      </c>
+      <c r="I16" s="1">
+        <f>[1]PAQUAY!$K$28</f>
+        <v>2.5972222222222223</v>
+      </c>
+      <c r="J16" s="1">
+        <f>[1]PAQUAY!$K$29</f>
+        <v>0.98611111111111127</v>
+      </c>
+      <c r="K16" s="1">
+        <f>[1]PAQUAY!$K$30</f>
+        <v>1.0625631313131314</v>
+      </c>
+      <c r="L16" s="1">
+        <f>[1]PAQUAY!$K$31</f>
+        <v>1.5361742424242426</v>
+      </c>
+      <c r="M16" s="1">
+        <f>[1]PAQUAY!$K$32</f>
+        <v>1.6597853535353537</v>
+      </c>
+      <c r="N16" s="1">
+        <f>[1]PAQUAY!$K$33</f>
+        <v>1.8472853535353537</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>24</v>
+      </c>
+      <c r="B17" s="1" t="str">
+        <f>[1]POIRET!$E$19</f>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="C17" s="1">
+        <f>[1]POIRET!$K$22</f>
+        <v>2.3513888888888888</v>
+      </c>
+      <c r="D17" s="1">
+        <f>[1]POIRET!$K$23</f>
+        <v>2.1055555555555552</v>
+      </c>
+      <c r="E17" s="1">
+        <f>[1]POIRET!$K$24</f>
+        <v>1.5201388888888885</v>
+      </c>
+      <c r="F17" s="1">
+        <f>[1]POIRET!$K$25</f>
+        <v>1.7604166666666663</v>
+      </c>
+      <c r="G17" s="1">
+        <f>[1]POIRET!$K$26</f>
+        <v>1.8298611111111107</v>
+      </c>
+      <c r="H17" s="1">
+        <f>[1]POIRET!$K$27</f>
+        <v>2.0874999999999999</v>
+      </c>
+      <c r="I17" s="1">
+        <f>[1]POIRET!$K$28</f>
+        <v>2.1506944444444445</v>
+      </c>
+      <c r="J17" s="1">
+        <f>[1]POIRET!$K$29</f>
+        <v>0.73541666666666661</v>
+      </c>
+      <c r="K17" s="1">
+        <f>[1]POIRET!$K$30</f>
+        <v>0.82222222222222219</v>
+      </c>
+      <c r="L17" s="1">
+        <f>[1]POIRET!$K$31</f>
+        <v>1.6166666666666667</v>
+      </c>
+      <c r="M17" s="1">
+        <f>[1]POIRET!$K$32</f>
+        <v>1.9333333333333333</v>
+      </c>
+      <c r="N17" s="1">
+        <f>[1]POIRET!$K$33</f>
+        <v>1.7097222222222221</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>25</v>
+      </c>
+      <c r="B18" s="1" t="str">
+        <f>[1]PRETTO!$E$19</f>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="C18" s="1">
+        <f>[1]PRETTO!$K$22</f>
+        <v>3.0159722222222225</v>
+      </c>
+      <c r="D18" s="1">
+        <f>[1]PRETTO!$K$23</f>
+        <v>2.7694444444444444</v>
+      </c>
+      <c r="E18" s="1">
+        <f>[1]PRETTO!$K$24</f>
+        <v>2.5458333333333329</v>
+      </c>
+      <c r="F18" s="1">
+        <f>[1]PRETTO!$K$25</f>
+        <v>2.9590277777777776</v>
+      </c>
+      <c r="G18" s="1">
+        <f>[1]PRETTO!$K$26</f>
+        <v>2.3874999999999997</v>
+      </c>
+      <c r="H18" s="1">
+        <f>[1]PRETTO!$K$27</f>
+        <v>1.9152777777777774</v>
+      </c>
+      <c r="I18" s="1">
+        <f>[1]PRETTO!$K$28</f>
+        <v>1.5423611111111106</v>
+      </c>
+      <c r="J18" s="1">
+        <f>[1]PRETTO!$K$29</f>
+        <v>1.6812499999999997</v>
+      </c>
+      <c r="K18" s="1">
+        <f>[1]PRETTO!$K$30</f>
+        <v>3.2993055555555553</v>
+      </c>
+      <c r="L18" s="1">
+        <f>[1]PRETTO!$K$31</f>
+        <v>5.374305555555555</v>
+      </c>
+      <c r="M18" s="1">
+        <f>[1]PRETTO!$K$32</f>
+        <v>4.8729166666666659</v>
+      </c>
+      <c r="N18" s="1">
+        <f>[1]PRETTO!$K$33</f>
+        <v>5.7562499999999996</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>26</v>
+      </c>
+      <c r="B19" s="1" t="str">
+        <f>[1]RENARD!$E$19</f>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="C19" s="1">
+        <f>[1]RENARD!$K$22</f>
+        <v>0.21590909090909091</v>
+      </c>
+      <c r="D19" s="1">
+        <f>[1]RENARD!$K$23</f>
+        <v>0.21313131313131314</v>
+      </c>
+      <c r="E19" s="1">
+        <f>[1]RENARD!$K$24</f>
+        <v>3.5353535353535331E-2</v>
+      </c>
+      <c r="F19" s="1">
+        <f>[1]RENARD!$K$25</f>
+        <v>-3.6075036075036093E-2</v>
+      </c>
+      <c r="G19" s="1">
+        <f>[1]RENARD!$K$26</f>
+        <v>5.5916305916305642E-3</v>
+      </c>
+      <c r="H19" s="1">
+        <f>[1]RENARD!$K$27</f>
+        <v>0.28333333333333333</v>
+      </c>
+      <c r="I19" s="1">
+        <f>[1]RENARD!$K$28</f>
+        <v>0.22979797979797981</v>
+      </c>
+      <c r="J19" s="1">
+        <f>[1]RENARD!$K$29</f>
+        <v>0.40965909090909092</v>
+      </c>
+      <c r="K19" s="1">
+        <f>[1]RENARD!$K$30</f>
+        <v>0.43428030303030302</v>
+      </c>
+      <c r="L19" s="1">
+        <f>[1]RENARD!$K$31</f>
+        <v>0.11830808080808081</v>
+      </c>
+      <c r="M19" s="1">
+        <f>[1]RENARD!$K$32</f>
+        <v>7.1969696969697017E-3</v>
+      </c>
+      <c r="N19" s="1">
+        <f>[1]RENARD!$K$33</f>
+        <v>4.9813928761297172E-2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>27</v>
+      </c>
+      <c r="B20" s="1">
+        <f>[1]STOURME!$E$19</f>
+        <v>1.1111111111111127E-2</v>
+      </c>
+      <c r="C20" s="1">
+        <f>[1]STOURME!$K$22</f>
+        <v>2.375</v>
+      </c>
+      <c r="D20" s="1">
+        <f>[1]STOURME!$K$23</f>
+        <v>2.4152777777777779</v>
+      </c>
+      <c r="E20" s="1">
+        <f>[1]STOURME!$K$24</f>
+        <v>2.5541666666666667</v>
+      </c>
+      <c r="F20" s="1">
+        <f>[1]STOURME!$K$25</f>
+        <v>2.5256944444444445</v>
+      </c>
+      <c r="G20" s="1">
+        <f>[1]STOURME!$K$26</f>
+        <v>2.4027777777777777</v>
+      </c>
+      <c r="H20" s="1">
+        <f>[1]STOURME!$K$27</f>
+        <v>2.6888888888888887</v>
+      </c>
+      <c r="I20" s="1">
+        <f>[1]STOURME!$K$28</f>
+        <v>2.7166666666666663</v>
+      </c>
+      <c r="J20" s="1">
+        <f>[1]STOURME!$K$29</f>
+        <v>2.5666666666666664</v>
+      </c>
+      <c r="K20" s="1">
+        <f>[1]STOURME!$K$30</f>
+        <v>2.5284722222222218</v>
+      </c>
+      <c r="L20" s="1">
+        <f>[1]STOURME!$K$31</f>
+        <v>2.4437499999999996</v>
+      </c>
+      <c r="M20" s="1">
+        <f>[1]STOURME!$K$32</f>
+        <v>2.4874999999999998</v>
+      </c>
+      <c r="N20" s="1">
+        <f>[1]STOURME!$K$33</f>
+        <v>2.40625</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>28</v>
+      </c>
+      <c r="B21" s="1" t="str">
+        <f>[1]VALDES!$E$19</f>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="C21" s="1">
+        <f>[1]VALDES!$K$22</f>
+        <v>0.17013888888888892</v>
+      </c>
+      <c r="D21" s="1">
+        <f>[1]VALDES!$K$23</f>
+        <v>0.38611111111111118</v>
+      </c>
+      <c r="E21" s="1">
+        <f>[1]VALDES!$K$24</f>
+        <v>0.14097222222222233</v>
+      </c>
+      <c r="F21" s="1">
+        <f>[1]VALDES!$K$25</f>
+        <v>0.30208333333333348</v>
+      </c>
+      <c r="G21" s="1">
+        <f>[1]VALDES!$K$26</f>
+        <v>0.32083333333333347</v>
+      </c>
+      <c r="H21" s="1">
+        <f>[1]VALDES!$K$27</f>
+        <v>0.53472222222222221</v>
+      </c>
+      <c r="I21" s="1">
+        <f>[1]VALDES!$K$28</f>
+        <v>0.70138888888888884</v>
+      </c>
+      <c r="J21" s="1">
+        <f>[1]VALDES!$K$29</f>
+        <v>0.89861111111111103</v>
+      </c>
+      <c r="K21" s="1">
+        <f>[1]VALDES!$K$30</f>
+        <v>0.80347222222222214</v>
+      </c>
+      <c r="L21" s="1">
+        <f>[1]VALDES!$K$31</f>
+        <v>1.0284722222222222</v>
+      </c>
+      <c r="M21" s="1">
+        <f>[1]VALDES!$K$32</f>
+        <v>1.0141666666666667</v>
+      </c>
+      <c r="N21" s="1">
+        <f>[1]VALDES!$K$33</f>
+        <v>0.83450000000000002</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:N21"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -2074,17 +4444,18 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="1af87cbf-0b42-4b26-9f6b-99e2f2c26033">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100937BC018F9DBE74C924557264AE521C8" ma:contentTypeVersion="11" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="df6304fc725e62364016da26349e6aa2">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="1af87cbf-0b42-4b26-9f6b-99e2f2c26033" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="24110c7d026aeb2113c3cc5af0e0c47a" ns2:_="">
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100937BC018F9DBE74C924557264AE521C8" ma:contentTypeVersion="11" ma:contentTypeDescription="Crée un document." ma:contentTypeScope="" ma:versionID="d3d2ccf64e0709aa15e389f389e88850">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="1af87cbf-0b42-4b26-9f6b-99e2f2c26033" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="c4eba4c6873b544fe67d9fa378d1b6dd" ns2:_="">
     <xsd:import namespace="1af87cbf-0b42-4b26-9f6b-99e2f2c26033"/>
     <xsd:element name="properties">
       <xsd:complexType>
@@ -2152,7 +4523,7 @@
         <xsd:restriction base="dms:Unknown"/>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="17" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="f5648a96-cea2-4c1b-af13-24c66345d7fe" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="17" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Balises d’images" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="f5648a96-cea2-4c1b-af13-24c66345d7fe" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
       <xsd:complexType>
         <xsd:sequence>
           <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
@@ -2176,8 +4547,8 @@
         <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
         <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
         <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Type de contenu"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Titre"/>
         <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
         <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
         <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
@@ -2267,42 +4638,15 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="1af87cbf-0b42-4b26-9f6b-99e2f2c26033">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3F5359EC-D85E-4EE8-994B-A84A38643895}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9D074922-0E66-4D1E-ACA7-53398BEE69CC}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="1af87cbf-0b42-4b26-9f6b-99e2f2c26033"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{43162B4C-8036-4FD3-B02E-9FAB6E06A7E9}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
@@ -2310,4 +4654,16 @@
     <ds:schemaRef ds:uri="1af87cbf-0b42-4b26-9f6b-99e2f2c26033"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{819F49E8-A739-4C91-9821-EBBA88D8F936}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3F5359EC-D85E-4EE8-994B-A84A38643895}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/data/HeureAdmin.xlsx
+++ b/data/HeureAdmin.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr date1904="1"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\deweba01\Downloads\files\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://fwb365.sharepoint.com/sites/CPM-PrestationsAgentsCPM/Shared Documents/Prestations Agents CPM/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C43EBD8-942C-4732-A3D9-C9D8A542A150}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="6" documentId="13_ncr:1_{8C43EBD8-942C-4732-A3D9-C9D8A542A150}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F0A67EC3-0316-4D22-AA5D-73DE03082E9D}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="2025" sheetId="2" r:id="rId1"/>
@@ -347,7 +347,12 @@
         </row>
         <row r="10">
           <cell r="K10">
-            <v>0.98353606226486145</v>
+            <v>0.99489969862849781</v>
+          </cell>
+        </row>
+        <row r="11">
+          <cell r="K11">
+            <v>0.66920525418405341</v>
           </cell>
         </row>
         <row r="19">
@@ -449,7 +454,12 @@
         </row>
         <row r="10">
           <cell r="K10">
-            <v>0.59656746031746033</v>
+            <v>0.85212301587301587</v>
+          </cell>
+        </row>
+        <row r="11">
+          <cell r="K11">
+            <v>0.58198412698412694</v>
           </cell>
         </row>
         <row r="19">
@@ -520,8 +530,8 @@
       </sheetData>
       <sheetData sheetId="2">
         <row r="2">
-          <cell r="F2">
-            <v>0.36438888888888887</v>
+          <cell r="F2" t="str">
+            <v xml:space="preserve"> </v>
           </cell>
         </row>
         <row r="5">
@@ -552,6 +562,11 @@
         <row r="10">
           <cell r="K10">
             <v>2.0004999999999997</v>
+          </cell>
+        </row>
+        <row r="11">
+          <cell r="K11">
+            <v>1.622722222222222</v>
           </cell>
         </row>
         <row r="19">
@@ -653,7 +668,12 @@
         </row>
         <row r="10">
           <cell r="K10">
-            <v>0.83581466842336394</v>
+            <v>0.95109244620114175</v>
+          </cell>
+        </row>
+        <row r="11">
+          <cell r="K11">
+            <v>0.98789800175669729</v>
           </cell>
         </row>
         <row r="19">
@@ -750,12 +770,17 @@
         </row>
         <row r="9">
           <cell r="K9">
-            <v>1.2145833333333331</v>
+            <v>1.1729166666666664</v>
           </cell>
         </row>
         <row r="10">
           <cell r="K10">
-            <v>0.99166666666666647</v>
+            <v>0.94999999999999973</v>
+          </cell>
+        </row>
+        <row r="11">
+          <cell r="K11">
+            <v>0.81874999999999976</v>
           </cell>
         </row>
         <row r="19">
@@ -860,6 +885,11 @@
             <v>5.2544191919191879E-2</v>
           </cell>
         </row>
+        <row r="11">
+          <cell r="K11">
+            <v>-0.65509469696969702</v>
+          </cell>
+        </row>
         <row r="19">
           <cell r="E19">
             <v>0</v>
@@ -912,6 +942,11 @@
             <v>0.84652118134647258</v>
           </cell>
         </row>
+        <row r="11">
+          <cell r="K11">
+            <v>0.43402118134647261</v>
+          </cell>
+        </row>
         <row r="19">
           <cell r="E19" t="str">
             <v xml:space="preserve"> </v>
@@ -1014,6 +1049,11 @@
             <v>0.70000000000000018</v>
           </cell>
         </row>
+        <row r="11">
+          <cell r="K11">
+            <v>0.66527777777777797</v>
+          </cell>
+        </row>
         <row r="19">
           <cell r="E19" t="str">
             <v xml:space="preserve"> </v>
@@ -1086,11 +1126,16 @@
             <v>0.25</v>
           </cell>
         </row>
+        <row r="11">
+          <cell r="K11">
+            <v>0.40833333333333333</v>
+          </cell>
+        </row>
       </sheetData>
       <sheetData sheetId="9">
         <row r="2">
           <cell r="F2">
-            <v>1.0763888888888888</v>
+            <v>0.85972222222222217</v>
           </cell>
         </row>
         <row r="5">
@@ -1123,6 +1168,11 @@
             <v>2.4746843434343435</v>
           </cell>
         </row>
+        <row r="11">
+          <cell r="K11">
+            <v>2.5080176767676767</v>
+          </cell>
+        </row>
         <row r="19">
           <cell r="E19" t="str">
             <v xml:space="preserve"> </v>
@@ -1191,8 +1241,8 @@
       </sheetData>
       <sheetData sheetId="10">
         <row r="2">
-          <cell r="F2">
-            <v>1.9340277777777777</v>
+          <cell r="F2" t="str">
+            <v xml:space="preserve"> </v>
           </cell>
         </row>
         <row r="5">
@@ -1222,7 +1272,12 @@
         </row>
         <row r="10">
           <cell r="K10">
-            <v>3.3840277777777779</v>
+            <v>3.2270833333333333</v>
+          </cell>
+        </row>
+        <row r="11">
+          <cell r="K11">
+            <v>1.4895833333333333</v>
           </cell>
         </row>
         <row r="19">
@@ -1327,6 +1382,11 @@
             <v>0.72844254080524107</v>
           </cell>
         </row>
+        <row r="11">
+          <cell r="K11">
+            <v>0.97844254080524107</v>
+          </cell>
+        </row>
         <row r="19">
           <cell r="E19" t="str">
             <v xml:space="preserve"> </v>
@@ -1396,12 +1456,17 @@
       <sheetData sheetId="12">
         <row r="9">
           <cell r="K9">
-            <v>0.20130718954248367</v>
+            <v>0.21527777777777779</v>
           </cell>
         </row>
         <row r="10">
           <cell r="K10">
-            <v>0.25711527035056447</v>
+            <v>0.29494949494949496</v>
+          </cell>
+        </row>
+        <row r="11">
+          <cell r="K11">
+            <v>0.38592171717171719</v>
           </cell>
         </row>
       </sheetData>
@@ -1441,6 +1506,11 @@
             <v>1.2388520799693574</v>
           </cell>
         </row>
+        <row r="11">
+          <cell r="K11">
+            <v>1.2714909688582463</v>
+          </cell>
+        </row>
         <row r="19">
           <cell r="E19" t="str">
             <v xml:space="preserve"> </v>
@@ -1509,8 +1579,8 @@
       </sheetData>
       <sheetData sheetId="14">
         <row r="2">
-          <cell r="F2">
-            <v>0.13964646464646485</v>
+          <cell r="F2" t="str">
+            <v xml:space="preserve"> </v>
           </cell>
         </row>
         <row r="5">
@@ -1541,6 +1611,11 @@
         <row r="10">
           <cell r="K10">
             <v>0.88964646464646524</v>
+          </cell>
+        </row>
+        <row r="11">
+          <cell r="K11">
+            <v>0.5632575757575764</v>
           </cell>
         </row>
         <row r="19">
@@ -1642,7 +1717,12 @@
         </row>
         <row r="10">
           <cell r="K10">
-            <v>0.64772727272727249</v>
+            <v>0.60606060606060574</v>
+          </cell>
+        </row>
+        <row r="11">
+          <cell r="K11">
+            <v>0.38244949494949465</v>
           </cell>
         </row>
         <row r="19">
@@ -1714,7 +1794,7 @@
       <sheetData sheetId="16">
         <row r="2">
           <cell r="F2">
-            <v>2.1722222222222216</v>
+            <v>2.1041666666666661</v>
           </cell>
         </row>
         <row r="5">
@@ -1745,6 +1825,11 @@
         <row r="10">
           <cell r="K10">
             <v>9.0388888888888896</v>
+          </cell>
+        </row>
+        <row r="11">
+          <cell r="K11">
+            <v>9.2208333333333332</v>
           </cell>
         </row>
         <row r="19">
@@ -1849,6 +1934,11 @@
             <v>0.24758629528366369</v>
           </cell>
         </row>
+        <row r="11">
+          <cell r="K11">
+            <v>0.41425296195033035</v>
+          </cell>
+        </row>
         <row r="19">
           <cell r="E19" t="str">
             <v xml:space="preserve"> </v>
@@ -1918,7 +2008,7 @@
       <sheetData sheetId="18">
         <row r="2">
           <cell r="F2">
-            <v>0.78541666666666676</v>
+            <v>0.24791666666666684</v>
           </cell>
         </row>
         <row r="5">
@@ -1948,7 +2038,12 @@
         </row>
         <row r="10">
           <cell r="K10">
-            <v>2.3584722222222219</v>
+            <v>2.3056944444444438</v>
+          </cell>
+        </row>
+        <row r="11">
+          <cell r="K11">
+            <v>2.0709722222222213</v>
           </cell>
         </row>
         <row r="19">
@@ -2050,7 +2145,12 @@
         </row>
         <row r="10">
           <cell r="K10">
-            <v>1.1276388888888891</v>
+            <v>1.1693055555555556</v>
+          </cell>
+        </row>
+        <row r="11">
+          <cell r="K11">
+            <v>1.3366666666666667</v>
           </cell>
         </row>
         <row r="19">
@@ -2129,21 +2229,21 @@
   <autoFilter ref="A1:N21" xr:uid="{C7300799-99B8-4EB6-AE56-6C90EDB091F8}"/>
   <tableColumns count="14">
     <tableColumn id="1" xr3:uid="{EB6C97B9-1CA8-48D2-9510-545DC67E1BBF}" name="Agent"/>
-    <tableColumn id="2" xr3:uid="{C66CE8F8-4087-4061-8EA3-AB9D0A8E447C}" name="Solde 31/08" dataDxfId="12"/>
-    <tableColumn id="7" xr3:uid="{9ECC8A47-2A4B-4D34-B13F-78D39587CA33}" name="Janvier" dataDxfId="11">
+    <tableColumn id="2" xr3:uid="{C66CE8F8-4087-4061-8EA3-AB9D0A8E447C}" name="Solde 31/08" dataDxfId="25"/>
+    <tableColumn id="7" xr3:uid="{9ECC8A47-2A4B-4D34-B13F-78D39587CA33}" name="Janvier" dataDxfId="24">
       <calculatedColumnFormula>[1]BLAVIER!$K$5</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{B672229B-47A9-4DDA-97B0-42F7FFE6755D}" name="Février" dataDxfId="10"/>
-    <tableColumn id="5" xr3:uid="{0D9FFA72-0E5C-462A-BC84-09657AFC2047}" name="Mars" dataDxfId="9"/>
-    <tableColumn id="6" xr3:uid="{6DD2E5EB-3749-4C8D-8925-14083FF7A139}" name="Avril" dataDxfId="8"/>
-    <tableColumn id="4" xr3:uid="{A20FEEC3-C73B-459B-97A2-74915F126C89}" name="Mai" dataDxfId="7"/>
-    <tableColumn id="3" xr3:uid="{8A000117-6DB3-4A3E-9E33-123A99327AE5}" name="Juin" dataDxfId="6"/>
-    <tableColumn id="9" xr3:uid="{0685936A-96FA-4393-87B0-7A35C9243EA4}" name="Juillet" dataDxfId="5"/>
-    <tableColumn id="10" xr3:uid="{70FA5B23-5F41-4134-AFA6-6CF2DBDA3A0B}" name="Août" dataDxfId="4"/>
-    <tableColumn id="11" xr3:uid="{5B0EE54E-7CF9-4BE7-98F7-31268BFF16C0}" name="Septembre" dataDxfId="3"/>
-    <tableColumn id="12" xr3:uid="{990F648E-0595-4475-9CA0-5C902A84D4D1}" name="Octobre" dataDxfId="2"/>
-    <tableColumn id="13" xr3:uid="{D412263F-C5F1-4334-8DE9-BAF8FA623F7F}" name="Novembre" dataDxfId="1"/>
-    <tableColumn id="14" xr3:uid="{A063487C-7F33-4DF7-8940-9A8E590D6F35}" name="Décembre" dataDxfId="0"/>
+    <tableColumn id="8" xr3:uid="{B672229B-47A9-4DDA-97B0-42F7FFE6755D}" name="Février" dataDxfId="23"/>
+    <tableColumn id="5" xr3:uid="{0D9FFA72-0E5C-462A-BC84-09657AFC2047}" name="Mars" dataDxfId="22"/>
+    <tableColumn id="6" xr3:uid="{6DD2E5EB-3749-4C8D-8925-14083FF7A139}" name="Avril" dataDxfId="21"/>
+    <tableColumn id="4" xr3:uid="{A20FEEC3-C73B-459B-97A2-74915F126C89}" name="Mai" dataDxfId="20"/>
+    <tableColumn id="3" xr3:uid="{8A000117-6DB3-4A3E-9E33-123A99327AE5}" name="Juin" dataDxfId="19"/>
+    <tableColumn id="9" xr3:uid="{0685936A-96FA-4393-87B0-7A35C9243EA4}" name="Juillet" dataDxfId="18"/>
+    <tableColumn id="10" xr3:uid="{70FA5B23-5F41-4134-AFA6-6CF2DBDA3A0B}" name="Août" dataDxfId="17"/>
+    <tableColumn id="11" xr3:uid="{5B0EE54E-7CF9-4BE7-98F7-31268BFF16C0}" name="Septembre" dataDxfId="16"/>
+    <tableColumn id="12" xr3:uid="{990F648E-0595-4475-9CA0-5C902A84D4D1}" name="Octobre" dataDxfId="15"/>
+    <tableColumn id="13" xr3:uid="{D412263F-C5F1-4334-8DE9-BAF8FA623F7F}" name="Novembre" dataDxfId="14"/>
+    <tableColumn id="14" xr3:uid="{A063487C-7F33-4DF7-8940-9A8E590D6F35}" name="Décembre" dataDxfId="13"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2154,21 +2254,21 @@
   <autoFilter ref="A1:N21" xr:uid="{C7300799-99B8-4EB6-AE56-6C90EDB091F8}"/>
   <tableColumns count="14">
     <tableColumn id="1" xr3:uid="{404799F8-EF23-44D1-82C6-A022BF0100EC}" name="Agent"/>
-    <tableColumn id="2" xr3:uid="{921AB302-A20C-46BE-9440-9E6AB6DAFD6C}" name="Solde 31/08" dataDxfId="25"/>
-    <tableColumn id="7" xr3:uid="{E374D505-F3A4-4A54-B661-7A811C5C6CF0}" name="Janvier" dataDxfId="24">
+    <tableColumn id="2" xr3:uid="{921AB302-A20C-46BE-9440-9E6AB6DAFD6C}" name="Solde 31/08" dataDxfId="12"/>
+    <tableColumn id="7" xr3:uid="{E374D505-F3A4-4A54-B661-7A811C5C6CF0}" name="Janvier" dataDxfId="11">
       <calculatedColumnFormula>[1]BLAVIER!$K$5</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{9D8E114C-EE46-411F-8DB7-F007D2820209}" name="Février" dataDxfId="23"/>
-    <tableColumn id="5" xr3:uid="{944F841B-7157-43A7-BBF4-EE37DB90304B}" name="Mars" dataDxfId="22"/>
-    <tableColumn id="6" xr3:uid="{D6979E67-6E41-4D87-8E2F-C77EC9B86F1C}" name="Avril" dataDxfId="21"/>
-    <tableColumn id="4" xr3:uid="{73890115-5FC3-4C52-9738-5535D8C89AA6}" name="Mai" dataDxfId="20"/>
-    <tableColumn id="3" xr3:uid="{C3AD0FE6-38FB-4AF2-A2FC-CD8C6AF1D34A}" name="Juin" dataDxfId="19"/>
-    <tableColumn id="9" xr3:uid="{2CF88554-1C99-48F6-A58C-B366489DC66A}" name="Juillet" dataDxfId="18"/>
-    <tableColumn id="10" xr3:uid="{92839190-8610-4DAD-9F46-735A99F92CBC}" name="Août" dataDxfId="17"/>
-    <tableColumn id="11" xr3:uid="{29BF599E-3D07-4D08-9AF4-0E200B9474AF}" name="Septembre" dataDxfId="16"/>
-    <tableColumn id="12" xr3:uid="{69B209A5-8270-436F-A131-3A88CE5DD18E}" name="Octobre" dataDxfId="15"/>
-    <tableColumn id="13" xr3:uid="{5495805F-AD9C-4F16-87DB-C13BD64B4392}" name="Novembre" dataDxfId="14"/>
-    <tableColumn id="14" xr3:uid="{4BC933CC-966E-4C7C-A940-6828309FC481}" name="Décembre" dataDxfId="13"/>
+    <tableColumn id="8" xr3:uid="{9D8E114C-EE46-411F-8DB7-F007D2820209}" name="Février" dataDxfId="10"/>
+    <tableColumn id="5" xr3:uid="{944F841B-7157-43A7-BBF4-EE37DB90304B}" name="Mars" dataDxfId="9"/>
+    <tableColumn id="6" xr3:uid="{D6979E67-6E41-4D87-8E2F-C77EC9B86F1C}" name="Avril" dataDxfId="8"/>
+    <tableColumn id="4" xr3:uid="{73890115-5FC3-4C52-9738-5535D8C89AA6}" name="Mai" dataDxfId="7"/>
+    <tableColumn id="3" xr3:uid="{C3AD0FE6-38FB-4AF2-A2FC-CD8C6AF1D34A}" name="Juin" dataDxfId="6"/>
+    <tableColumn id="9" xr3:uid="{2CF88554-1C99-48F6-A58C-B366489DC66A}" name="Juillet" dataDxfId="0"/>
+    <tableColumn id="10" xr3:uid="{92839190-8610-4DAD-9F46-735A99F92CBC}" name="Août" dataDxfId="5"/>
+    <tableColumn id="11" xr3:uid="{29BF599E-3D07-4D08-9AF4-0E200B9474AF}" name="Septembre" dataDxfId="4"/>
+    <tableColumn id="12" xr3:uid="{69B209A5-8270-436F-A131-3A88CE5DD18E}" name="Octobre" dataDxfId="3"/>
+    <tableColumn id="13" xr3:uid="{5495805F-AD9C-4F16-87DB-C13BD64B4392}" name="Novembre" dataDxfId="2"/>
+    <tableColumn id="14" xr3:uid="{4BC933CC-966E-4C7C-A940-6828309FC481}" name="Décembre" dataDxfId="1"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -3714,9 +3814,12 @@
       </c>
       <c r="H2" s="1">
         <f>[1]BECKERS!$K$10</f>
-        <v>0.98353606226486145</v>
-      </c>
-      <c r="I2" s="1"/>
+        <v>0.99489969862849781</v>
+      </c>
+      <c r="I2" s="1">
+        <f>[1]BECKERS!$K$11</f>
+        <v>0.66920525418405341</v>
+      </c>
       <c r="J2" s="1"/>
       <c r="K2" s="1"/>
       <c r="L2" s="1"/>
@@ -3753,9 +3856,12 @@
       </c>
       <c r="H3" s="1">
         <f>[1]BLAVIER!$K$10</f>
-        <v>0.59656746031746033</v>
-      </c>
-      <c r="I3" s="1"/>
+        <v>0.85212301587301587</v>
+      </c>
+      <c r="I3" s="1">
+        <f>[1]BLAVIER!$K$11</f>
+        <v>0.58198412698412694</v>
+      </c>
       <c r="J3" s="1"/>
       <c r="K3" s="1"/>
       <c r="L3" s="1"/>
@@ -3766,9 +3872,9 @@
       <c r="A4" t="s">
         <v>14</v>
       </c>
-      <c r="B4" s="1">
+      <c r="B4" s="1" t="str">
         <f>[1]BREUCKER!$F$2</f>
-        <v>0.36438888888888887</v>
+        <v xml:space="preserve"> </v>
       </c>
       <c r="C4" s="1">
         <f>[1]BREUCKER!$K$5</f>
@@ -3794,7 +3900,10 @@
         <f>[1]BREUCKER!$K$10</f>
         <v>2.0004999999999997</v>
       </c>
-      <c r="I4" s="1"/>
+      <c r="I4" s="1">
+        <f>[1]BREUCKER!$K$11</f>
+        <v>1.622722222222222</v>
+      </c>
       <c r="J4" s="1"/>
       <c r="K4" s="1"/>
       <c r="L4" s="1"/>
@@ -3831,9 +3940,12 @@
       </c>
       <c r="H5" s="1">
         <f>[1]BRUNIN!$K$10</f>
-        <v>0.83581466842336394</v>
-      </c>
-      <c r="I5" s="1"/>
+        <v>0.95109244620114175</v>
+      </c>
+      <c r="I5" s="1">
+        <f>[1]BRUNIN!$K$11</f>
+        <v>0.98789800175669729</v>
+      </c>
       <c r="J5" s="1"/>
       <c r="K5" s="1"/>
       <c r="L5" s="1"/>
@@ -3866,13 +3978,16 @@
       </c>
       <c r="G6" s="1">
         <f>[1]DEWEZ!$K$9</f>
-        <v>1.2145833333333331</v>
+        <v>1.1729166666666664</v>
       </c>
       <c r="H6" s="1">
         <f>[1]DEWEZ!$K$10</f>
-        <v>0.99166666666666647</v>
-      </c>
-      <c r="I6" s="1"/>
+        <v>0.94999999999999973</v>
+      </c>
+      <c r="I6" s="1">
+        <f>[1]DEWEZ!$K$11</f>
+        <v>0.81874999999999976</v>
+      </c>
       <c r="J6" s="1"/>
       <c r="K6" s="1"/>
       <c r="L6" s="1"/>
@@ -3911,7 +4026,10 @@
         <f>[1]HENDRICKX!$K$10</f>
         <v>5.2544191919191879E-2</v>
       </c>
-      <c r="I7" s="1"/>
+      <c r="I7" s="1">
+        <f>[1]HENDRICKX!$K$11</f>
+        <v>-0.65509469696969702</v>
+      </c>
       <c r="J7" s="1"/>
       <c r="K7" s="1"/>
       <c r="L7" s="1"/>
@@ -3950,7 +4068,10 @@
         <f>[1]HOEBEKE!$K$10</f>
         <v>0.84652118134647258</v>
       </c>
-      <c r="I8" s="1"/>
+      <c r="I8" s="1">
+        <f>[1]HOEBEKE!$K$11</f>
+        <v>0.43402118134647261</v>
+      </c>
       <c r="J8" s="1"/>
       <c r="K8" s="1"/>
       <c r="L8" s="1"/>
@@ -3989,7 +4110,10 @@
         <f>[1]JOIRIS!$K$10</f>
         <v>0.70000000000000018</v>
       </c>
-      <c r="I9" s="1"/>
+      <c r="I9" s="1">
+        <f>[1]JOIRIS!$K$11</f>
+        <v>0.66527777777777797</v>
+      </c>
       <c r="J9" s="1"/>
       <c r="K9" s="1"/>
       <c r="L9" s="1"/>
@@ -4010,7 +4134,10 @@
         <f>[1]KAISER!$K$10</f>
         <v>0.25</v>
       </c>
-      <c r="I10" s="1"/>
+      <c r="I10" s="1">
+        <f>[1]KAISER!$K$11</f>
+        <v>0.40833333333333333</v>
+      </c>
       <c r="J10" s="1"/>
       <c r="K10" s="1"/>
       <c r="L10" s="1"/>
@@ -4023,7 +4150,7 @@
       </c>
       <c r="B11" s="1">
         <f>[1]LAMBERT!$F$2</f>
-        <v>1.0763888888888888</v>
+        <v>0.85972222222222217</v>
       </c>
       <c r="C11" s="1">
         <f>[1]LAMBERT!$K$5</f>
@@ -4049,7 +4176,10 @@
         <f>[1]LAMBERT!$K$10</f>
         <v>2.4746843434343435</v>
       </c>
-      <c r="I11" s="1"/>
+      <c r="I11" s="1">
+        <f>[1]LAMBERT!$K$11</f>
+        <v>2.5080176767676767</v>
+      </c>
       <c r="J11" s="1"/>
       <c r="K11" s="1"/>
       <c r="L11" s="1"/>
@@ -4060,9 +4190,9 @@
       <c r="A12" t="s">
         <v>20</v>
       </c>
-      <c r="B12" s="1">
+      <c r="B12" s="1" t="str">
         <f>[1]LEBOUTTE!$F$2</f>
-        <v>1.9340277777777777</v>
+        <v xml:space="preserve"> </v>
       </c>
       <c r="C12" s="1">
         <f>[1]LEBOUTTE!$K$5</f>
@@ -4086,9 +4216,12 @@
       </c>
       <c r="H12" s="1">
         <f>[1]LEBOUTTE!$K$10</f>
-        <v>3.3840277777777779</v>
-      </c>
-      <c r="I12" s="1"/>
+        <v>3.2270833333333333</v>
+      </c>
+      <c r="I12" s="1">
+        <f>[1]LEBOUTTE!$K$11</f>
+        <v>1.4895833333333333</v>
+      </c>
       <c r="J12" s="1"/>
       <c r="K12" s="1"/>
       <c r="L12" s="1"/>
@@ -4127,7 +4260,10 @@
         <f>[1]MAGNUS!$K$10</f>
         <v>0.72844254080524107</v>
       </c>
-      <c r="I13" s="1"/>
+      <c r="I13" s="1">
+        <f>[1]MAGNUS!$K$11</f>
+        <v>0.97844254080524107</v>
+      </c>
       <c r="J13" s="1"/>
       <c r="K13" s="1"/>
       <c r="L13" s="1"/>
@@ -4145,13 +4281,16 @@
       <c r="F14" s="1"/>
       <c r="G14" s="1">
         <f>[1]NDEMA!$K$9</f>
-        <v>0.20130718954248367</v>
+        <v>0.21527777777777779</v>
       </c>
       <c r="H14" s="1">
         <f>[1]NDEMA!$K$10</f>
-        <v>0.25711527035056447</v>
-      </c>
-      <c r="I14" s="1"/>
+        <v>0.29494949494949496</v>
+      </c>
+      <c r="I14" s="1">
+        <f>[1]NDEMA!$K$11</f>
+        <v>0.38592171717171719</v>
+      </c>
       <c r="J14" s="1"/>
       <c r="K14" s="1"/>
       <c r="L14" s="1"/>
@@ -4190,7 +4329,10 @@
         <f>[1]NOLET!$K$10</f>
         <v>1.2388520799693574</v>
       </c>
-      <c r="I15" s="1"/>
+      <c r="I15" s="1">
+        <f>[1]NOLET!$K$11</f>
+        <v>1.2714909688582463</v>
+      </c>
       <c r="J15" s="1"/>
       <c r="K15" s="1"/>
       <c r="L15" s="1"/>
@@ -4201,9 +4343,9 @@
       <c r="A16" t="s">
         <v>23</v>
       </c>
-      <c r="B16" s="1">
+      <c r="B16" s="1" t="str">
         <f>[1]PAQUAY!$F$2</f>
-        <v>0.13964646464646485</v>
+        <v xml:space="preserve"> </v>
       </c>
       <c r="C16" s="1">
         <f>[1]PAQUAY!$K$5</f>
@@ -4229,7 +4371,10 @@
         <f>[1]PAQUAY!$K$10</f>
         <v>0.88964646464646524</v>
       </c>
-      <c r="I16" s="1"/>
+      <c r="I16" s="1">
+        <f>[1]PAQUAY!$K$11</f>
+        <v>0.5632575757575764</v>
+      </c>
       <c r="J16" s="1"/>
       <c r="K16" s="1"/>
       <c r="L16" s="1"/>
@@ -4266,9 +4411,12 @@
       </c>
       <c r="H17" s="1">
         <f>[1]POIRET!$K$10</f>
-        <v>0.64772727272727249</v>
-      </c>
-      <c r="I17" s="1"/>
+        <v>0.60606060606060574</v>
+      </c>
+      <c r="I17" s="1">
+        <f>[1]POIRET!$K$11</f>
+        <v>0.38244949494949465</v>
+      </c>
       <c r="J17" s="1"/>
       <c r="K17" s="1"/>
       <c r="L17" s="1"/>
@@ -4281,7 +4429,7 @@
       </c>
       <c r="B18" s="1">
         <f>[1]PRETTO!$F$2</f>
-        <v>2.1722222222222216</v>
+        <v>2.1041666666666661</v>
       </c>
       <c r="C18" s="1">
         <f>[1]PRETTO!$K$5</f>
@@ -4307,7 +4455,10 @@
         <f>[1]PRETTO!$K$10</f>
         <v>9.0388888888888896</v>
       </c>
-      <c r="I18" s="1"/>
+      <c r="I18" s="1">
+        <f>[1]PRETTO!$K$11</f>
+        <v>9.2208333333333332</v>
+      </c>
       <c r="J18" s="1"/>
       <c r="K18" s="1"/>
       <c r="L18" s="1"/>
@@ -4346,7 +4497,10 @@
         <f>[1]RENARD!$K$10</f>
         <v>0.24758629528366369</v>
       </c>
-      <c r="I19" s="1"/>
+      <c r="I19" s="1">
+        <f>[1]RENARD!$K$11</f>
+        <v>0.41425296195033035</v>
+      </c>
       <c r="J19" s="1"/>
       <c r="K19" s="1"/>
       <c r="L19" s="1"/>
@@ -4359,7 +4513,7 @@
       </c>
       <c r="B20" s="1">
         <f>[1]STOURME!$F$2</f>
-        <v>0.78541666666666676</v>
+        <v>0.24791666666666684</v>
       </c>
       <c r="C20" s="1">
         <f>[1]STOURME!$K$5</f>
@@ -4383,9 +4537,12 @@
       </c>
       <c r="H20" s="1">
         <f>[1]STOURME!$K$10</f>
-        <v>2.3584722222222219</v>
-      </c>
-      <c r="I20" s="1"/>
+        <v>2.3056944444444438</v>
+      </c>
+      <c r="I20" s="1">
+        <f>[1]STOURME!$K$11</f>
+        <v>2.0709722222222213</v>
+      </c>
       <c r="J20" s="1"/>
       <c r="K20" s="1"/>
       <c r="L20" s="1"/>
@@ -4422,9 +4579,12 @@
       </c>
       <c r="H21" s="1">
         <f>[1]VALDES!$K$10</f>
-        <v>1.1276388888888891</v>
-      </c>
-      <c r="I21" s="1"/>
+        <v>1.1693055555555556</v>
+      </c>
+      <c r="I21" s="1">
+        <f>[1]VALDES!$K$11</f>
+        <v>1.3366666666666667</v>
+      </c>
       <c r="J21" s="1"/>
       <c r="K21" s="1"/>
       <c r="L21" s="1"/>
@@ -4454,8 +4614,8 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100937BC018F9DBE74C924557264AE521C8" ma:contentTypeVersion="11" ma:contentTypeDescription="Crée un document." ma:contentTypeScope="" ma:versionID="d3d2ccf64e0709aa15e389f389e88850">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="1af87cbf-0b42-4b26-9f6b-99e2f2c26033" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="c4eba4c6873b544fe67d9fa378d1b6dd" ns2:_="">
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100937BC018F9DBE74C924557264AE521C8" ma:contentTypeVersion="11" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="df6304fc725e62364016da26349e6aa2">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="1af87cbf-0b42-4b26-9f6b-99e2f2c26033" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="24110c7d026aeb2113c3cc5af0e0c47a" ns2:_="">
     <xsd:import namespace="1af87cbf-0b42-4b26-9f6b-99e2f2c26033"/>
     <xsd:element name="properties">
       <xsd:complexType>
@@ -4523,7 +4683,7 @@
         <xsd:restriction base="dms:Unknown"/>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="17" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Balises d’images" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="f5648a96-cea2-4c1b-af13-24c66345d7fe" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="17" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="f5648a96-cea2-4c1b-af13-24c66345d7fe" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
       <xsd:complexType>
         <xsd:sequence>
           <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
@@ -4547,8 +4707,8 @@
         <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
         <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
         <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Type de contenu"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Titre"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
         <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
         <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
         <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
@@ -4657,7 +4817,7 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{819F49E8-A739-4C91-9821-EBBA88D8F936}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{69449F73-ECCA-4049-9F77-5F6BD292D3D4}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>

--- a/data/HeureAdmin.xlsx
+++ b/data/HeureAdmin.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://fwb365.sharepoint.com/sites/CPM-PrestationsAgentsCPM/Shared Documents/Prestations Agents CPM/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="6" documentId="13_ncr:1_{8C43EBD8-942C-4732-A3D9-C9D8A542A150}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F0A67EC3-0316-4D22-AA5D-73DE03082E9D}"/>
+  <xr:revisionPtr revIDLastSave="8" documentId="13_ncr:1_{8C43EBD8-942C-4732-A3D9-C9D8A542A150}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{21C0B190-C45F-4648-AA5D-E835E7955CB0}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="2025" sheetId="2" r:id="rId1"/>
@@ -566,7 +566,7 @@
         </row>
         <row r="11">
           <cell r="K11">
-            <v>1.622722222222222</v>
+            <v>1.6560555555555554</v>
           </cell>
         </row>
         <row r="19">
@@ -2229,21 +2229,21 @@
   <autoFilter ref="A1:N21" xr:uid="{C7300799-99B8-4EB6-AE56-6C90EDB091F8}"/>
   <tableColumns count="14">
     <tableColumn id="1" xr3:uid="{EB6C97B9-1CA8-48D2-9510-545DC67E1BBF}" name="Agent"/>
-    <tableColumn id="2" xr3:uid="{C66CE8F8-4087-4061-8EA3-AB9D0A8E447C}" name="Solde 31/08" dataDxfId="25"/>
-    <tableColumn id="7" xr3:uid="{9ECC8A47-2A4B-4D34-B13F-78D39587CA33}" name="Janvier" dataDxfId="24">
+    <tableColumn id="2" xr3:uid="{C66CE8F8-4087-4061-8EA3-AB9D0A8E447C}" name="Solde 31/08" dataDxfId="12"/>
+    <tableColumn id="7" xr3:uid="{9ECC8A47-2A4B-4D34-B13F-78D39587CA33}" name="Janvier" dataDxfId="11">
       <calculatedColumnFormula>[1]BLAVIER!$K$5</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{B672229B-47A9-4DDA-97B0-42F7FFE6755D}" name="Février" dataDxfId="23"/>
-    <tableColumn id="5" xr3:uid="{0D9FFA72-0E5C-462A-BC84-09657AFC2047}" name="Mars" dataDxfId="22"/>
-    <tableColumn id="6" xr3:uid="{6DD2E5EB-3749-4C8D-8925-14083FF7A139}" name="Avril" dataDxfId="21"/>
-    <tableColumn id="4" xr3:uid="{A20FEEC3-C73B-459B-97A2-74915F126C89}" name="Mai" dataDxfId="20"/>
-    <tableColumn id="3" xr3:uid="{8A000117-6DB3-4A3E-9E33-123A99327AE5}" name="Juin" dataDxfId="19"/>
-    <tableColumn id="9" xr3:uid="{0685936A-96FA-4393-87B0-7A35C9243EA4}" name="Juillet" dataDxfId="18"/>
-    <tableColumn id="10" xr3:uid="{70FA5B23-5F41-4134-AFA6-6CF2DBDA3A0B}" name="Août" dataDxfId="17"/>
-    <tableColumn id="11" xr3:uid="{5B0EE54E-7CF9-4BE7-98F7-31268BFF16C0}" name="Septembre" dataDxfId="16"/>
-    <tableColumn id="12" xr3:uid="{990F648E-0595-4475-9CA0-5C902A84D4D1}" name="Octobre" dataDxfId="15"/>
-    <tableColumn id="13" xr3:uid="{D412263F-C5F1-4334-8DE9-BAF8FA623F7F}" name="Novembre" dataDxfId="14"/>
-    <tableColumn id="14" xr3:uid="{A063487C-7F33-4DF7-8940-9A8E590D6F35}" name="Décembre" dataDxfId="13"/>
+    <tableColumn id="8" xr3:uid="{B672229B-47A9-4DDA-97B0-42F7FFE6755D}" name="Février" dataDxfId="10"/>
+    <tableColumn id="5" xr3:uid="{0D9FFA72-0E5C-462A-BC84-09657AFC2047}" name="Mars" dataDxfId="9"/>
+    <tableColumn id="6" xr3:uid="{6DD2E5EB-3749-4C8D-8925-14083FF7A139}" name="Avril" dataDxfId="8"/>
+    <tableColumn id="4" xr3:uid="{A20FEEC3-C73B-459B-97A2-74915F126C89}" name="Mai" dataDxfId="7"/>
+    <tableColumn id="3" xr3:uid="{8A000117-6DB3-4A3E-9E33-123A99327AE5}" name="Juin" dataDxfId="6"/>
+    <tableColumn id="9" xr3:uid="{0685936A-96FA-4393-87B0-7A35C9243EA4}" name="Juillet" dataDxfId="5"/>
+    <tableColumn id="10" xr3:uid="{70FA5B23-5F41-4134-AFA6-6CF2DBDA3A0B}" name="Août" dataDxfId="4"/>
+    <tableColumn id="11" xr3:uid="{5B0EE54E-7CF9-4BE7-98F7-31268BFF16C0}" name="Septembre" dataDxfId="3"/>
+    <tableColumn id="12" xr3:uid="{990F648E-0595-4475-9CA0-5C902A84D4D1}" name="Octobre" dataDxfId="2"/>
+    <tableColumn id="13" xr3:uid="{D412263F-C5F1-4334-8DE9-BAF8FA623F7F}" name="Novembre" dataDxfId="1"/>
+    <tableColumn id="14" xr3:uid="{A063487C-7F33-4DF7-8940-9A8E590D6F35}" name="Décembre" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2254,21 +2254,21 @@
   <autoFilter ref="A1:N21" xr:uid="{C7300799-99B8-4EB6-AE56-6C90EDB091F8}"/>
   <tableColumns count="14">
     <tableColumn id="1" xr3:uid="{404799F8-EF23-44D1-82C6-A022BF0100EC}" name="Agent"/>
-    <tableColumn id="2" xr3:uid="{921AB302-A20C-46BE-9440-9E6AB6DAFD6C}" name="Solde 31/08" dataDxfId="12"/>
-    <tableColumn id="7" xr3:uid="{E374D505-F3A4-4A54-B661-7A811C5C6CF0}" name="Janvier" dataDxfId="11">
+    <tableColumn id="2" xr3:uid="{921AB302-A20C-46BE-9440-9E6AB6DAFD6C}" name="Solde 31/08" dataDxfId="25"/>
+    <tableColumn id="7" xr3:uid="{E374D505-F3A4-4A54-B661-7A811C5C6CF0}" name="Janvier" dataDxfId="24">
       <calculatedColumnFormula>[1]BLAVIER!$K$5</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{9D8E114C-EE46-411F-8DB7-F007D2820209}" name="Février" dataDxfId="10"/>
-    <tableColumn id="5" xr3:uid="{944F841B-7157-43A7-BBF4-EE37DB90304B}" name="Mars" dataDxfId="9"/>
-    <tableColumn id="6" xr3:uid="{D6979E67-6E41-4D87-8E2F-C77EC9B86F1C}" name="Avril" dataDxfId="8"/>
-    <tableColumn id="4" xr3:uid="{73890115-5FC3-4C52-9738-5535D8C89AA6}" name="Mai" dataDxfId="7"/>
-    <tableColumn id="3" xr3:uid="{C3AD0FE6-38FB-4AF2-A2FC-CD8C6AF1D34A}" name="Juin" dataDxfId="6"/>
-    <tableColumn id="9" xr3:uid="{2CF88554-1C99-48F6-A58C-B366489DC66A}" name="Juillet" dataDxfId="0"/>
-    <tableColumn id="10" xr3:uid="{92839190-8610-4DAD-9F46-735A99F92CBC}" name="Août" dataDxfId="5"/>
-    <tableColumn id="11" xr3:uid="{29BF599E-3D07-4D08-9AF4-0E200B9474AF}" name="Septembre" dataDxfId="4"/>
-    <tableColumn id="12" xr3:uid="{69B209A5-8270-436F-A131-3A88CE5DD18E}" name="Octobre" dataDxfId="3"/>
-    <tableColumn id="13" xr3:uid="{5495805F-AD9C-4F16-87DB-C13BD64B4392}" name="Novembre" dataDxfId="2"/>
-    <tableColumn id="14" xr3:uid="{4BC933CC-966E-4C7C-A940-6828309FC481}" name="Décembre" dataDxfId="1"/>
+    <tableColumn id="8" xr3:uid="{9D8E114C-EE46-411F-8DB7-F007D2820209}" name="Février" dataDxfId="23"/>
+    <tableColumn id="5" xr3:uid="{944F841B-7157-43A7-BBF4-EE37DB90304B}" name="Mars" dataDxfId="22"/>
+    <tableColumn id="6" xr3:uid="{D6979E67-6E41-4D87-8E2F-C77EC9B86F1C}" name="Avril" dataDxfId="21"/>
+    <tableColumn id="4" xr3:uid="{73890115-5FC3-4C52-9738-5535D8C89AA6}" name="Mai" dataDxfId="20"/>
+    <tableColumn id="3" xr3:uid="{C3AD0FE6-38FB-4AF2-A2FC-CD8C6AF1D34A}" name="Juin" dataDxfId="19"/>
+    <tableColumn id="9" xr3:uid="{2CF88554-1C99-48F6-A58C-B366489DC66A}" name="Juillet" dataDxfId="18"/>
+    <tableColumn id="10" xr3:uid="{92839190-8610-4DAD-9F46-735A99F92CBC}" name="Août" dataDxfId="17"/>
+    <tableColumn id="11" xr3:uid="{29BF599E-3D07-4D08-9AF4-0E200B9474AF}" name="Septembre" dataDxfId="16"/>
+    <tableColumn id="12" xr3:uid="{69B209A5-8270-436F-A131-3A88CE5DD18E}" name="Octobre" dataDxfId="15"/>
+    <tableColumn id="13" xr3:uid="{5495805F-AD9C-4F16-87DB-C13BD64B4392}" name="Novembre" dataDxfId="14"/>
+    <tableColumn id="14" xr3:uid="{4BC933CC-966E-4C7C-A940-6828309FC481}" name="Décembre" dataDxfId="13"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -3902,7 +3902,7 @@
       </c>
       <c r="I4" s="1">
         <f>[1]BREUCKER!$K$11</f>
-        <v>1.622722222222222</v>
+        <v>1.6560555555555554</v>
       </c>
       <c r="J4" s="1"/>
       <c r="K4" s="1"/>
@@ -4604,13 +4604,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="1af87cbf-0b42-4b26-9f6b-99e2f2c26033">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -4798,15 +4797,42 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="1af87cbf-0b42-4b26-9f6b-99e2f2c26033">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3F5359EC-D85E-4EE8-994B-A84A38643895}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{69449F73-ECCA-4049-9F77-5F6BD292D3D4}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="1af87cbf-0b42-4b26-9f6b-99e2f2c26033"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{43162B4C-8036-4FD3-B02E-9FAB6E06A7E9}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
@@ -4814,16 +4840,4 @@
     <ds:schemaRef ds:uri="1af87cbf-0b42-4b26-9f6b-99e2f2c26033"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{69449F73-ECCA-4049-9F77-5F6BD292D3D4}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3F5359EC-D85E-4EE8-994B-A84A38643895}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>